--- a/operatori.xlsx
+++ b/operatori.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivanc\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivanc\OneDrive\Desktop\manutenzione_web\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="2370" windowHeight="555"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12870"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="3" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="100">
   <si>
     <t>Borriello Pasquale</t>
   </si>
@@ -318,6 +318,12 @@
   </si>
   <si>
     <t>Codice</t>
+  </si>
+  <si>
+    <t>Colantuono</t>
+  </si>
+  <si>
+    <t>sitav8103</t>
   </si>
 </sst>
 </file>
@@ -377,7 +383,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -400,6 +406,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -410,7 +427,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -437,6 +454,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -721,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
@@ -1235,6 +1258,14 @@
         <v>82</v>
       </c>
     </row>
+    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B47" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/operatori.xlsx
+++ b/operatori.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="101">
   <si>
     <t>Borriello Pasquale</t>
   </si>
@@ -324,6 +324,9 @@
   </si>
   <si>
     <t>sitav8103</t>
+  </si>
+  <si>
+    <t>Telefono</t>
   </si>
 </sst>
 </file>
@@ -427,7 +430,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -462,6 +465,8 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -744,15 +749,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>95</v>
       </c>
@@ -762,8 +768,11 @@
       <c r="C1" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -773,8 +782,11 @@
       <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D2" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -784,8 +796,11 @@
       <c r="C3" s="9" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D3" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -795,8 +810,11 @@
       <c r="C4" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D4" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -806,8 +824,11 @@
       <c r="C5" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D5" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -817,8 +838,11 @@
       <c r="C6" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D6" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -828,8 +852,11 @@
       <c r="C7" s="5" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D7" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -839,8 +866,11 @@
       <c r="C8" s="1" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D8" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>2</v>
       </c>
@@ -850,8 +880,11 @@
       <c r="C9" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D9" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -861,8 +894,11 @@
       <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D10" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -872,8 +908,11 @@
       <c r="C11" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D11" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -883,8 +922,11 @@
       <c r="C12" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D12" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -894,8 +936,11 @@
       <c r="C13" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D13" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -905,8 +950,11 @@
       <c r="C14" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D14" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -916,8 +964,11 @@
       <c r="C15" s="5" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D15" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -927,8 +978,11 @@
       <c r="C16" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D16" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -938,8 +992,11 @@
       <c r="C17" s="1" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D17" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -949,8 +1006,11 @@
       <c r="C18" s="1" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D18" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -960,8 +1020,11 @@
       <c r="C19" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D19" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -971,8 +1034,11 @@
       <c r="C20" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D20" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -982,8 +1048,11 @@
       <c r="C21" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D21" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -993,8 +1062,11 @@
       <c r="C22" s="8" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D22" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -1004,8 +1076,11 @@
       <c r="C23" s="3" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D23" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -1015,8 +1090,11 @@
       <c r="C24" s="5" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D24" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -1026,8 +1104,11 @@
       <c r="C25" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D25" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1037,8 +1118,11 @@
       <c r="C26" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D26" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -1048,8 +1132,11 @@
       <c r="C27" s="1" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D27" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -1059,8 +1146,11 @@
       <c r="C28" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D28" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -1070,8 +1160,11 @@
       <c r="C29" s="7" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D29" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -1081,8 +1174,11 @@
       <c r="C30" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D30" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -1092,8 +1188,11 @@
       <c r="C31" s="5" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D31" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -1103,8 +1202,11 @@
       <c r="C32" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D32" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -1114,8 +1216,11 @@
       <c r="C33" s="5" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D33" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -1125,8 +1230,11 @@
       <c r="C34" s="5" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D34" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -1136,8 +1244,11 @@
       <c r="C35" s="1" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D35" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -1147,8 +1258,11 @@
       <c r="C36" s="5" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D36" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -1158,8 +1272,11 @@
       <c r="C37" s="1" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D37" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -1169,8 +1286,11 @@
       <c r="C38" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D38" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -1180,8 +1300,11 @@
       <c r="C39" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D39" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -1191,8 +1314,11 @@
       <c r="C40" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D40" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -1202,8 +1328,11 @@
       <c r="C41" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D41" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -1213,8 +1342,11 @@
       <c r="C42" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D42" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -1224,8 +1356,11 @@
       <c r="C43" s="6" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D43" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1370,11 @@
       <c r="C44" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D44" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -1246,8 +1384,11 @@
       <c r="C45" s="1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D45" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -1257,16 +1398,26 @@
       <c r="C46" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D46" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B47" s="10" t="s">
         <v>98</v>
       </c>
       <c r="C47" s="11" t="s">
         <v>99</v>
       </c>
+      <c r="D47" s="12">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="51" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F51" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/operatori.xlsx
+++ b/operatori.xlsx
@@ -783,7 +783,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="12">
-        <v>393477618059</v>
+        <v>393457186030</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -797,7 +797,7 @@
         <v>18</v>
       </c>
       <c r="D3" s="12">
-        <v>393477618059</v>
+        <v>393477748517</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -811,7 +811,7 @@
         <v>38</v>
       </c>
       <c r="D4" s="12">
-        <v>393477618059</v>
+        <v>393338751617</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -825,7 +825,7 @@
         <v>46</v>
       </c>
       <c r="D5" s="12">
-        <v>393477618059</v>
+        <v>393472634487</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">

--- a/operatori.xlsx
+++ b/operatori.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="107">
   <si>
     <t>Borriello Pasquale</t>
   </si>
@@ -327,6 +327,24 @@
   </si>
   <si>
     <t>Telefono</t>
+  </si>
+  <si>
+    <t>Dentice</t>
+  </si>
+  <si>
+    <t>Correttiva</t>
+  </si>
+  <si>
+    <t>Cioffi</t>
+  </si>
+  <si>
+    <t>Basco</t>
+  </si>
+  <si>
+    <t>Coo. Prog.</t>
+  </si>
+  <si>
+    <t>Coo. Corr.</t>
   </si>
 </sst>
 </file>
@@ -372,7 +390,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -382,6 +400,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -430,7 +454,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -467,6 +491,8 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -838,7 +864,7 @@
       <c r="C6" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="14">
         <v>393477618059</v>
       </c>
     </row>
@@ -853,7 +879,7 @@
         <v>64</v>
       </c>
       <c r="D7" s="12">
-        <v>393477618059</v>
+        <v>393388867929</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -867,7 +893,7 @@
         <v>72</v>
       </c>
       <c r="D8" s="12">
-        <v>393477618059</v>
+        <v>393924426156</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -895,7 +921,7 @@
         <v>10</v>
       </c>
       <c r="D10" s="12">
-        <v>393477618059</v>
+        <v>393312365048</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -909,7 +935,7 @@
         <v>20</v>
       </c>
       <c r="D11" s="12">
-        <v>393477618059</v>
+        <v>393381449666</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -923,7 +949,7 @@
         <v>30</v>
       </c>
       <c r="D12" s="12">
-        <v>393477618059</v>
+        <v>393294285283</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -937,7 +963,7 @@
         <v>40</v>
       </c>
       <c r="D13" s="12">
-        <v>393477618059</v>
+        <v>393348446091</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -950,7 +976,7 @@
       <c r="C14" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="14">
         <v>393477618059</v>
       </c>
     </row>
@@ -965,7 +991,7 @@
         <v>56</v>
       </c>
       <c r="D15" s="12">
-        <v>393477618059</v>
+        <v>393349016062</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1287,7 +1313,7 @@
         <v>16</v>
       </c>
       <c r="D38" s="12">
-        <v>393477618059</v>
+        <v>393516843447</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1301,7 +1327,7 @@
         <v>26</v>
       </c>
       <c r="D39" s="12">
-        <v>393477618059</v>
+        <v>393382798808</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1371,7 +1397,7 @@
         <v>1</v>
       </c>
       <c r="D44" s="12">
-        <v>393477618059</v>
+        <v>393334360904</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -1413,7 +1439,40 @@
         <v>393477618059</v>
       </c>
     </row>
-    <row r="51" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>106</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D48" s="12">
+        <v>393926352302</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>102</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D49" s="15">
+        <v>393475623576</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>105</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D50" s="15">
+        <v>393515994998</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F51" s="13"/>
     </row>
   </sheetData>

--- a/operatori.xlsx
+++ b/operatori.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="111">
   <si>
     <t>Borriello Pasquale</t>
   </si>
@@ -345,6 +345,18 @@
   </si>
   <si>
     <t>Coo. Corr.</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>Ruolo</t>
+  </si>
+  <si>
+    <t>caposquadra</t>
+  </si>
+  <si>
+    <t>operatore</t>
   </si>
 </sst>
 </file>
@@ -410,7 +422,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -433,17 +445,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -454,7 +455,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -483,16 +484,11 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -778,28 +774,37 @@
   <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="10"/>
+    <col min="6" max="6" width="12.140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="10" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="E1" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -808,12 +813,18 @@
       <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="11">
         <v>393457186030</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="E2" s="10">
+        <v>1234</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -822,12 +833,18 @@
       <c r="C3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="11">
         <v>393477748517</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="E3" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -836,12 +853,18 @@
       <c r="C4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="11">
         <v>393338751617</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="E4" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -850,12 +873,18 @@
       <c r="C5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="11">
         <v>393472634487</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="E5" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -864,12 +893,18 @@
       <c r="C6" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D6" s="14">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="D6" s="12">
+        <v>393477618059</v>
+      </c>
+      <c r="E6" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -878,12 +913,18 @@
       <c r="C7" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="11">
         <v>393388867929</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="E7" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
         <v>2</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -892,12 +933,18 @@
       <c r="C8" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11">
         <v>393924426156</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="E8" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
         <v>2</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -906,12 +953,18 @@
       <c r="C9" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="D9" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E9" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -920,12 +973,18 @@
       <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11">
         <v>393312365048</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="E10" s="10">
+        <v>1234</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -934,12 +993,18 @@
       <c r="C11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11">
         <v>393381449666</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="E11" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
         <v>3</v>
       </c>
       <c r="B12" s="5" t="s">
@@ -948,12 +1013,18 @@
       <c r="C12" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="11">
         <v>393294285283</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="E12" s="10">
+        <v>1234</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
         <v>3</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -962,12 +1033,18 @@
       <c r="C13" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="11">
         <v>393348446091</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="E13" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
         <v>3</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -976,12 +1053,18 @@
       <c r="C14" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="14">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="D14" s="12">
+        <v>393477618059</v>
+      </c>
+      <c r="E14" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
         <v>3</v>
       </c>
       <c r="B15" s="5" t="s">
@@ -990,12 +1073,18 @@
       <c r="C15" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="11">
         <v>393349016062</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="E15" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
         <v>3</v>
       </c>
       <c r="B16" s="5" t="s">
@@ -1004,12 +1093,18 @@
       <c r="C16" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D16" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="D16" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E16" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
         <v>3</v>
       </c>
       <c r="B17" s="5" t="s">
@@ -1018,12 +1113,18 @@
       <c r="C17" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="D17" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E17" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -1032,12 +1133,18 @@
       <c r="C18" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D18" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="D18" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E18" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
         <v>4</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -1046,12 +1153,18 @@
       <c r="C19" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="D19" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E19" s="10">
+        <v>1234</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
         <v>4</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -1060,12 +1173,18 @@
       <c r="C20" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="D20" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E20" s="10">
+        <v>1234</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
         <v>4</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -1074,12 +1193,18 @@
       <c r="C21" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="D21" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E21" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
         <v>4</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -1088,12 +1213,18 @@
       <c r="C22" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="D22" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="D22" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E22" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
         <v>4</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -1102,12 +1233,18 @@
       <c r="C23" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D23" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="D23" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E23" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
         <v>4</v>
       </c>
       <c r="B24" s="5" t="s">
@@ -1116,12 +1253,18 @@
       <c r="C24" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D24" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="D24" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E24" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="10" t="s">
         <v>4</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -1130,12 +1273,18 @@
       <c r="C25" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D25" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="D25" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E25" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
         <v>4</v>
       </c>
       <c r="B26" s="5" t="s">
@@ -1144,12 +1293,18 @@
       <c r="C26" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D26" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="D26" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E26" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
         <v>4</v>
       </c>
       <c r="B27" s="5" t="s">
@@ -1158,12 +1313,18 @@
       <c r="C27" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D27" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="D27" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E27" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -1172,12 +1333,18 @@
       <c r="C28" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D28" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="D28" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E28" s="10">
+        <v>1234</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B29" s="7" t="s">
@@ -1186,12 +1353,18 @@
       <c r="C29" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="D29" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E29" s="10">
+        <v>1234</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -1200,12 +1373,18 @@
       <c r="C30" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D30" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="D30" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E30" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B31" s="5" t="s">
@@ -1214,12 +1393,18 @@
       <c r="C31" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D31" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="D31" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E31" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -1228,12 +1413,18 @@
       <c r="C32" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D32" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="D32" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E32" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B33" s="5" t="s">
@@ -1242,12 +1433,18 @@
       <c r="C33" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D33" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="D33" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E33" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B34" s="5" t="s">
@@ -1256,12 +1453,18 @@
       <c r="C34" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D34" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="D34" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E34" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B35" s="5" t="s">
@@ -1270,12 +1473,18 @@
       <c r="C35" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D35" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="D35" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E35" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B36" s="5" t="s">
@@ -1284,12 +1493,18 @@
       <c r="C36" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="D36" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="D36" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E36" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B37" s="5" t="s">
@@ -1298,12 +1513,18 @@
       <c r="C37" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D37" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="D37" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E37" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -1312,12 +1533,18 @@
       <c r="C38" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D38" s="12">
+      <c r="D38" s="11">
         <v>393516843447</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="E38" s="10">
+        <v>1234</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B39" s="3" t="s">
@@ -1326,12 +1553,18 @@
       <c r="C39" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D39" s="12">
+      <c r="D39" s="11">
         <v>393382798808</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="E39" s="10">
+        <v>1234</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B40" s="3" t="s">
@@ -1340,12 +1573,18 @@
       <c r="C40" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D40" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="D40" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E40" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -1354,12 +1593,18 @@
       <c r="C41" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="D41" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E41" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B42" s="3" t="s">
@@ -1368,12 +1613,18 @@
       <c r="C42" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D42" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="D42" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E42" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A43" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B43" s="5" t="s">
@@ -1382,12 +1633,18 @@
       <c r="C43" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D43" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="D43" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E43" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B44" s="5" t="s">
@@ -1396,12 +1653,18 @@
       <c r="C44" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D44" s="12">
+      <c r="D44" s="11">
         <v>393334360904</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="E44" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B45" s="5" t="s">
@@ -1410,12 +1673,18 @@
       <c r="C45" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D45" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="D45" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E45" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B46" s="5" t="s">
@@ -1424,56 +1693,62 @@
       <c r="C46" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D46" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B47" s="10" t="s">
+      <c r="D46" s="11">
+        <v>393477618059</v>
+      </c>
+      <c r="E46" s="10">
+        <v>1111</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B47" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D47" s="12">
-        <v>393477618059</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="D47" s="11">
+        <v>393477618059</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="B48" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D48" s="12">
+      <c r="D48" s="11">
         <v>393926352302</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="A49" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B49" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="D49" s="15">
+      <c r="D49" s="13">
         <v>393475623576</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="A50" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B50" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D50" s="15">
+      <c r="D50" s="13">
         <v>393515994998</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F51" s="13"/>
+      <c r="F51" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/operatori.xlsx
+++ b/operatori.xlsx
@@ -1176,2074 +1176,2073 @@
   <dimension ref="A1:F123"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="1"/>
-    <col min="6" max="6" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="5" width="11" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>97</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>104</v>
-      </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>8</v>
       </c>
       <c r="D2" s="2">
         <v>393457186030</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1">
         <v>1234</v>
       </c>
-      <c r="F2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>18</v>
       </c>
       <c r="D3" s="2">
         <v>393477748517</v>
       </c>
-      <c r="E3" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>105</v>
+      <c r="E3" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>38</v>
       </c>
       <c r="D4" s="2">
         <v>393338751617</v>
       </c>
-      <c r="E4" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>106</v>
+      <c r="E4" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>46</v>
       </c>
       <c r="D5" s="2">
         <v>393472634487</v>
       </c>
-      <c r="E5" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>106</v>
+      <c r="E5" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>54</v>
       </c>
       <c r="D6" s="3">
         <v>393477618059</v>
       </c>
-      <c r="E6" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>106</v>
+      <c r="E6" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>64</v>
       </c>
       <c r="D7" s="2">
         <v>393388867929</v>
       </c>
-      <c r="E7" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>106</v>
+      <c r="E7" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>72</v>
       </c>
       <c r="D8" s="2">
         <v>393924426156</v>
       </c>
-      <c r="E8" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>106</v>
+      <c r="E8" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>86</v>
       </c>
       <c r="D9" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E9" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>106</v>
+      <c r="E9" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>10</v>
       </c>
       <c r="D10" s="2">
         <v>393312365048</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="1">
         <v>1234</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>105</v>
-      </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>20</v>
       </c>
       <c r="D11" s="2">
         <v>393381449666</v>
       </c>
-      <c r="E11" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>106</v>
+      <c r="E11" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>30</v>
       </c>
       <c r="D12" s="2">
         <v>393294285283</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="1">
         <v>1234</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>105</v>
-      </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>40</v>
       </c>
       <c r="D13" s="2">
         <v>393348446091</v>
       </c>
-      <c r="E13" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>106</v>
+      <c r="E13" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>48</v>
       </c>
       <c r="D14" s="3">
         <v>393477618059</v>
       </c>
-      <c r="E14" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>106</v>
+      <c r="E14" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>56</v>
       </c>
       <c r="D15" s="2">
         <v>393349016062</v>
       </c>
-      <c r="E15" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>106</v>
+      <c r="E15" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>88</v>
       </c>
       <c r="D16" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E16" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>106</v>
+      <c r="E16" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>80</v>
       </c>
       <c r="D17" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E17" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>106</v>
+      <c r="E17" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>76</v>
       </c>
       <c r="D18" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E18" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>106</v>
+      <c r="E18" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>12</v>
       </c>
       <c r="D19" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="1">
         <v>1234</v>
       </c>
-      <c r="F19" s="1" t="s">
+    </row>
+    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+      <c r="C20" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>22</v>
       </c>
       <c r="D20" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="1">
         <v>1234</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>105</v>
-      </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>32</v>
       </c>
       <c r="D21" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E21" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>106</v>
+      <c r="E21" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>70</v>
       </c>
       <c r="D22" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E22" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>106</v>
+      <c r="E22" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>58</v>
       </c>
       <c r="D23" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E23" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>106</v>
+      <c r="E23" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>66</v>
       </c>
       <c r="D24" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E24" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>106</v>
+      <c r="E24" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>28</v>
       </c>
       <c r="D25" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E25" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>106</v>
+      <c r="E25" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>92</v>
       </c>
       <c r="D26" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E26" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>106</v>
+      <c r="E26" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>81</v>
       </c>
       <c r="D27" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E27" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>106</v>
+      <c r="E27" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>14</v>
       </c>
       <c r="D28" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E28" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="1">
         <v>1234</v>
       </c>
-      <c r="F28" s="1" t="s">
+    </row>
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="C29" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>24</v>
       </c>
       <c r="D29" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E29" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="1">
         <v>1234</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>105</v>
-      </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>42</v>
       </c>
       <c r="D30" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E30" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>106</v>
+      <c r="E30" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>50</v>
       </c>
       <c r="D31" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E31" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>106</v>
+      <c r="E31" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>34</v>
       </c>
       <c r="D32" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E32" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>106</v>
+      <c r="E32" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>60</v>
       </c>
       <c r="D33" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E33" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>106</v>
+      <c r="E33" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="F33" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>68</v>
       </c>
       <c r="D34" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E34" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>106</v>
+      <c r="E34" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="F34" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>90</v>
       </c>
       <c r="D35" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E35" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>106</v>
+      <c r="E35" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F35" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>73</v>
       </c>
       <c r="D36" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E36" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>106</v>
+      <c r="E36" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F36" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>84</v>
       </c>
       <c r="D37" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E37" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>106</v>
+      <c r="E37" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="F37" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>16</v>
       </c>
       <c r="D38" s="2">
         <v>393516843447</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E38" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F38" s="1">
         <v>1234</v>
       </c>
-      <c r="F38" s="1" t="s">
+    </row>
+    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="16" t="s">
-        <v>26</v>
       </c>
       <c r="D39" s="2">
         <v>393382798808</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E39" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F39" s="1">
         <v>1234</v>
       </c>
-      <c r="F39" s="1" t="s">
-        <v>105</v>
-      </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C40" s="17" t="s">
-        <v>36</v>
       </c>
       <c r="D40" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E40" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>106</v>
+      <c r="E40" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F40" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>44</v>
       </c>
       <c r="D41" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E41" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>106</v>
+      <c r="E41" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="F41" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C42" s="15" t="s">
-        <v>52</v>
       </c>
       <c r="D42" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E42" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>106</v>
+      <c r="E42" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="F42" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C43" s="21" t="s">
-        <v>62</v>
       </c>
       <c r="D43" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E43" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>106</v>
+      <c r="E43" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="F43" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>1</v>
       </c>
       <c r="D44" s="2">
         <v>393334360904</v>
       </c>
-      <c r="E44" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>106</v>
+      <c r="E44" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="F44" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>94</v>
       </c>
       <c r="D45" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E45" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>106</v>
+      <c r="E45" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="F45" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C46" s="13" t="s">
-        <v>82</v>
       </c>
       <c r="D46" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E46" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>106</v>
+      <c r="E46" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="F46" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B47" s="8" t="s">
+      <c r="A47" s="8" t="s">
         <v>107</v>
-      </c>
-      <c r="C47" s="13" t="s">
-        <v>98</v>
       </c>
       <c r="D47" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E47" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="F47" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>108</v>
       </c>
       <c r="D48" s="2">
         <v>393926352302</v>
       </c>
-      <c r="E48" s="1">
+      <c r="F48" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>110</v>
       </c>
       <c r="D49" s="4">
         <v>393475623576</v>
       </c>
-      <c r="E49" s="1">
+      <c r="F49" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>109</v>
       </c>
       <c r="D50" s="4">
         <v>393515994998</v>
       </c>
-      <c r="E50" s="1">
+      <c r="F50" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B51" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C51" s="13" t="s">
+      <c r="E51" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="E51" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F51" s="5" t="s">
+      <c r="F51" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A52" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="B52" s="5" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
+      <c r="C52" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B52" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="C52" s="17" t="s">
+      <c r="E52" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="E52" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F52" s="5" t="s">
+      <c r="F52" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E53" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="F53" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E54" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="F54" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E55" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="F55" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A56" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F56" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A57" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E57" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="F57" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A58" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="F58" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="F59" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A60" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="F60" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A61" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E61" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F61" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A62" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F62" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A63" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B53" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="C53" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="E53" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B54" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="C54" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="E54" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B55" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="C55" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="E55" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B56" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="C56" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="E56" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B57" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="C57" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="E57" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B58" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="C58" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E58" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B59" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="C59" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="E59" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B60" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="C60" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="E60" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B61" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="C61" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="E61" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B62" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="C62" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="E62" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
+      <c r="C63" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B63" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="C63" s="17" t="s">
+      <c r="E63" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="E63" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F63" s="1" t="s">
+      <c r="F63" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A64" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
+      <c r="C64" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B64" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="C64" s="13" t="s">
+      <c r="E64" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="E64" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F64" s="1" t="s">
+      <c r="F64" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A65" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E65" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="F65" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A66" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F66" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A67" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E67" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="F67" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A68" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E68" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="F68" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A69" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="F69" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A70" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="F70" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A71" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E71" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="F71" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A72" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E72" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="F72" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A73" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E73" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="F73" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A74" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="F74" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A75" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B65" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="C65" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="E65" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B66" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="C66" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="E66" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B67" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="C67" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="E67" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B68" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="C68" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="E68" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B69" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="C69" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="E69" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B70" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="C70" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="E70" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B71" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="C71" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="E71" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B72" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="C72" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="E72" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B73" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="C73" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="E73" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B74" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="C74" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="E74" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
+      <c r="C75" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B75" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="C75" s="13" t="s">
+      <c r="E75" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="E75" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F75" s="1" t="s">
+      <c r="F75" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A76" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="F76" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A77" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E77" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="F77" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A78" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E78" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="F78" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A79" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E79" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="F79" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A80" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E80" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="F80" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A81" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E81" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="F81" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A82" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E82" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="F82" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A83" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
+      <c r="C83" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B76" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="C76" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="E76" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
+      <c r="E83" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="F83" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A84" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B77" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="C77" s="16" t="s">
-        <v>166</v>
-      </c>
-      <c r="E77" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
+      <c r="E84" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="F84" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A85" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B78" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="C78" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="E78" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
+      <c r="E85" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="F85" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A86" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B79" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="C79" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="E79" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
+      <c r="E86" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="F86" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A87" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B80" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="C80" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="E80" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B81" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="C81" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="E81" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B82" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="C82" s="16" t="s">
-        <v>176</v>
-      </c>
-      <c r="E82" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B83" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="C83" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="E83" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F83" s="1" t="s">
+      <c r="E87" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="F87" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A88" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B84" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="C84" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="E84" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B85" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="C85" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="E85" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B86" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="C86" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="E86" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B87" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="C87" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="E87" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
+      <c r="C88" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B88" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="C88" s="16" t="s">
-        <v>189</v>
       </c>
       <c r="D88" s="2">
         <v>393297735084</v>
       </c>
-      <c r="E88" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F88" s="1" t="s">
+      <c r="E88" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="F88" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A89" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
+      <c r="C89" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B89" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="C89" s="13" t="s">
-        <v>191</v>
       </c>
       <c r="D89" s="2">
         <v>393281527839</v>
       </c>
-      <c r="E89" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>105</v>
+      <c r="E89" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="F89" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
+      <c r="A90" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C90" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B90" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="C90" s="17" t="s">
-        <v>193</v>
       </c>
       <c r="D90" s="2">
         <v>393337039626</v>
       </c>
-      <c r="E90" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>106</v>
+      <c r="E90" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="F90" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
+      <c r="A91" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C91" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B91" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="C91" s="17" t="s">
-        <v>195</v>
       </c>
       <c r="D91" s="2">
         <v>393668993714</v>
       </c>
-      <c r="E91" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>106</v>
+      <c r="E91" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="F91" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
+      <c r="A92" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C92" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B92" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="C92" s="13" t="s">
-        <v>197</v>
       </c>
       <c r="D92" s="2">
         <v>393273997950</v>
       </c>
-      <c r="E92" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>106</v>
+      <c r="E92" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="F92" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
+      <c r="A93" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B93" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="C93" s="13" t="s">
-        <v>199</v>
       </c>
       <c r="D93" s="2">
         <v>393316298506</v>
       </c>
-      <c r="E93" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>106</v>
+      <c r="E93" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="F93" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
+      <c r="A94" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C94" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B94" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="C94" s="13" t="s">
-        <v>201</v>
       </c>
       <c r="D94" s="2">
         <v>393343140500</v>
       </c>
-      <c r="E94" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>106</v>
+      <c r="E94" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="F94" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
+      <c r="A95" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B95" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="C95" s="16" t="s">
-        <v>203</v>
       </c>
       <c r="D95" s="2">
         <v>393351612468</v>
       </c>
-      <c r="E95" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>106</v>
+      <c r="E95" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="F95" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
+      <c r="A96" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B96" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="C96" s="15" t="s">
-        <v>205</v>
       </c>
       <c r="D96" s="2">
         <v>393402901672</v>
       </c>
-      <c r="E96" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>106</v>
+      <c r="E96" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="F96" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
+      <c r="A97" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C97" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B97" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="C97" s="13" t="s">
-        <v>207</v>
       </c>
       <c r="D97" s="2">
         <v>393510837400</v>
       </c>
-      <c r="E97" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>106</v>
+      <c r="E97" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="F97" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
+      <c r="A98" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C98" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B98" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="C98" s="13" t="s">
-        <v>209</v>
       </c>
       <c r="D98" s="2">
         <v>393421215671</v>
       </c>
-      <c r="E98" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>106</v>
+      <c r="E98" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="F98" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
+      <c r="A99" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C99" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B99" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="C99" s="13" t="s">
-        <v>211</v>
       </c>
       <c r="D99" s="2">
         <v>393313969976</v>
       </c>
-      <c r="E99" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>106</v>
+      <c r="E99" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="F99" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
+      <c r="A100" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C100" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B100" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="C100" s="13" t="s">
+      <c r="D100" s="2"/>
+      <c r="E100" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="D100" s="2"/>
-      <c r="E100" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F100" s="1" t="s">
+      <c r="F100" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A101" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="101" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
+      <c r="C101" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B101" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="C101" s="13" t="s">
+      <c r="D101" s="2"/>
+      <c r="E101" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="D101" s="2"/>
-      <c r="E101" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>105</v>
+      <c r="F101" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
+      <c r="A102" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C102" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B102" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="C102" s="13" t="s">
+      <c r="D102" s="2"/>
+      <c r="E102" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="D102" s="2"/>
-      <c r="E102" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>106</v>
+      <c r="F102" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
+      <c r="A103" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B103" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="C103" s="18" t="s">
+      <c r="D103" s="2"/>
+      <c r="E103" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="D103" s="2"/>
-      <c r="E103" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>106</v>
+      <c r="F103" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
+      <c r="A104" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B104" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="C104" s="13" t="s">
+      <c r="D104" s="2"/>
+      <c r="E104" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="D104" s="2"/>
-      <c r="E104" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>106</v>
+      <c r="F104" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
+      <c r="A105" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B105" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="C105" s="13" t="s">
+      <c r="D105" s="2"/>
+      <c r="E105" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="D105" s="2"/>
-      <c r="E105" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>106</v>
+      <c r="F105" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A106" s="1" t="s">
+      <c r="A106" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C106" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B106" s="15" t="s">
-        <v>225</v>
-      </c>
-      <c r="C106" s="15" t="s">
+      <c r="D106" s="2"/>
+      <c r="E106" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="D106" s="2"/>
-      <c r="E106" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>106</v>
+      <c r="F106" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A107" s="1" t="s">
+      <c r="A107" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C107" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B107" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="C107" s="13" t="s">
+      <c r="D107" s="2"/>
+      <c r="E107" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="D107" s="2"/>
-      <c r="E107" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>106</v>
+      <c r="F107" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A108" s="1" t="s">
+      <c r="A108" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C108" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B108" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="C108" s="13" t="s">
+      <c r="D108" s="2"/>
+      <c r="E108" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="D108" s="2"/>
-      <c r="E108" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>106</v>
+      <c r="F108" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
+      <c r="A109" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C109" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B109" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="C109" s="20" t="s">
+      <c r="D109" s="2"/>
+      <c r="E109" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="D109" s="2"/>
-      <c r="E109" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>106</v>
+      <c r="F109" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A110" s="1" t="s">
+      <c r="A110" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C110" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B110" s="15" t="s">
-        <v>233</v>
-      </c>
-      <c r="C110" s="13" t="s">
+      <c r="D110" s="2"/>
+      <c r="E110" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="D110" s="2"/>
-      <c r="E110" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>106</v>
+      <c r="F110" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A111" s="1" t="s">
+      <c r="A111" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C111" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B111" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="C111" s="13" t="s">
+      <c r="D111" s="2"/>
+      <c r="E111" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="D111" s="2"/>
-      <c r="E111" s="1">
-        <v>1111</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>106</v>
+      <c r="F111" s="1">
+        <v>1111</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">

--- a/operatori.xlsx
+++ b/operatori.xlsx
@@ -47,9 +47,6 @@
     <t>Squadra prog. 5 H24</t>
   </si>
   <si>
-    <t>Lettieri Alessandro</t>
-  </si>
-  <si>
     <t>sitav231</t>
   </si>
   <si>
@@ -77,9 +74,6 @@
     <t>elar626</t>
   </si>
   <si>
-    <t>Sibilio Raffaele</t>
-  </si>
-  <si>
     <t>sitav8125</t>
   </si>
   <si>
@@ -137,9 +131,6 @@
     <t>sitav1149</t>
   </si>
   <si>
-    <t>Bellezza Pasquale</t>
-  </si>
-  <si>
     <t>sitav8003</t>
   </si>
   <si>
@@ -161,9 +152,6 @@
     <t>sitav8185</t>
   </si>
   <si>
-    <t>Fontemagi Fabio</t>
-  </si>
-  <si>
     <t>sitav8041</t>
   </si>
   <si>
@@ -185,9 +173,6 @@
     <t>sitav8329</t>
   </si>
   <si>
-    <t>Manzo Giovanni</t>
-  </si>
-  <si>
     <t>elar6131</t>
   </si>
   <si>
@@ -215,9 +200,6 @@
     <t>sitav8225</t>
   </si>
   <si>
-    <t>Marrazzo Pietro</t>
-  </si>
-  <si>
     <t>sitav8264</t>
   </si>
   <si>
@@ -239,9 +221,6 @@
     <t>sitav8224</t>
   </si>
   <si>
-    <t>Panico Daniele</t>
-  </si>
-  <si>
     <t>sitav8263</t>
   </si>
   <si>
@@ -281,9 +260,6 @@
     <t>elar6249</t>
   </si>
   <si>
-    <t>Guerriero Vincenzo</t>
-  </si>
-  <si>
     <t>sitav1136</t>
   </si>
   <si>
@@ -738,6 +714,30 @@
   </si>
   <si>
     <t>Squadra corr. 5 H24</t>
+  </si>
+  <si>
+    <t>lettieri</t>
+  </si>
+  <si>
+    <t>sibilio</t>
+  </si>
+  <si>
+    <t>bellezza</t>
+  </si>
+  <si>
+    <t>fontemagi</t>
+  </si>
+  <si>
+    <t>manzo</t>
+  </si>
+  <si>
+    <t>marrazzo</t>
+  </si>
+  <si>
+    <t>panico</t>
+  </si>
+  <si>
+    <t>guerriero</t>
   </si>
 </sst>
 </file>
@@ -1186,30 +1186,30 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="C1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>7</v>
+        <v>230</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
@@ -1218,7 +1218,7 @@
         <v>393457186030</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" s="1">
         <v>1234</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2</v>
@@ -1238,7 +1238,7 @@
         <v>393477748517</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F3" s="1">
         <v>1111</v>
@@ -1246,10 +1246,10 @@
     </row>
     <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>37</v>
+        <v>232</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>2</v>
@@ -1258,7 +1258,7 @@
         <v>393338751617</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F4" s="1">
         <v>1111</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>45</v>
+        <v>233</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>2</v>
@@ -1278,7 +1278,7 @@
         <v>393472634487</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F5" s="1">
         <v>1111</v>
@@ -1286,10 +1286,10 @@
     </row>
     <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>53</v>
+        <v>234</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>2</v>
@@ -1298,7 +1298,7 @@
         <v>393477618059</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F6" s="1">
         <v>1111</v>
@@ -1306,10 +1306,10 @@
     </row>
     <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>63</v>
+        <v>235</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>2</v>
@@ -1318,7 +1318,7 @@
         <v>393388867929</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F7" s="1">
         <v>1111</v>
@@ -1326,10 +1326,10 @@
     </row>
     <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>71</v>
+        <v>236</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>2</v>
@@ -1338,7 +1338,7 @@
         <v>393924426156</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F8" s="1">
         <v>1111</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>85</v>
+        <v>237</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>2</v>
@@ -1358,7 +1358,7 @@
         <v>393477618059</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F9" s="1">
         <v>1111</v>
@@ -1366,10 +1366,10 @@
     </row>
     <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -1378,7 +1378,7 @@
         <v>393312365048</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" s="1">
         <v>1234</v>
@@ -1386,10 +1386,10 @@
     </row>
     <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1398,7 +1398,7 @@
         <v>393381449666</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F11" s="1">
         <v>1111</v>
@@ -1406,10 +1406,10 @@
     </row>
     <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1418,7 +1418,7 @@
         <v>393294285283</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F12" s="1">
         <v>1234</v>
@@ -1426,10 +1426,10 @@
     </row>
     <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1438,7 +1438,7 @@
         <v>393348446091</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F13" s="1">
         <v>1111</v>
@@ -1446,10 +1446,10 @@
     </row>
     <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1458,7 +1458,7 @@
         <v>393477618059</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F14" s="1">
         <v>1111</v>
@@ -1466,10 +1466,10 @@
     </row>
     <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -1478,7 +1478,7 @@
         <v>393349016062</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F15" s="1">
         <v>1111</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1498,7 +1498,7 @@
         <v>393477618059</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="F16" s="1">
         <v>1111</v>
@@ -1506,10 +1506,10 @@
     </row>
     <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1518,7 +1518,7 @@
         <v>393477618059</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="F17" s="1">
         <v>1111</v>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1538,7 +1538,7 @@
         <v>393477618059</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F18" s="1">
         <v>1111</v>
@@ -1546,10 +1546,10 @@
     </row>
     <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>4</v>
@@ -1558,7 +1558,7 @@
         <v>393477618059</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F19" s="1">
         <v>1234</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>4</v>
@@ -1578,7 +1578,7 @@
         <v>393477618059</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F20" s="1">
         <v>1234</v>
@@ -1586,10 +1586,10 @@
     </row>
     <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>4</v>
@@ -1598,7 +1598,7 @@
         <v>393477618059</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F21" s="1">
         <v>1111</v>
@@ -1606,10 +1606,10 @@
     </row>
     <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>4</v>
@@ -1618,7 +1618,7 @@
         <v>393477618059</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F22" s="1">
         <v>1111</v>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>4</v>
@@ -1638,7 +1638,7 @@
         <v>393477618059</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F23" s="1">
         <v>1111</v>
@@ -1646,10 +1646,10 @@
     </row>
     <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>4</v>
@@ -1658,7 +1658,7 @@
         <v>393477618059</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F24" s="1">
         <v>1111</v>
@@ -1666,10 +1666,10 @@
     </row>
     <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>4</v>
@@ -1678,7 +1678,7 @@
         <v>393477618059</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F25" s="1">
         <v>1111</v>
@@ -1686,10 +1686,10 @@
     </row>
     <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>4</v>
@@ -1698,7 +1698,7 @@
         <v>393477618059</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F26" s="1">
         <v>1111</v>
@@ -1706,10 +1706,10 @@
     </row>
     <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>4</v>
@@ -1718,7 +1718,7 @@
         <v>393477618059</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F27" s="1">
         <v>1111</v>
@@ -1726,10 +1726,10 @@
     </row>
     <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>5</v>
@@ -1738,7 +1738,7 @@
         <v>393477618059</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F28" s="1">
         <v>1234</v>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>5</v>
@@ -1758,7 +1758,7 @@
         <v>393477618059</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F29" s="1">
         <v>1234</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>5</v>
@@ -1778,7 +1778,7 @@
         <v>393477618059</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F30" s="1">
         <v>1111</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>5</v>
@@ -1798,7 +1798,7 @@
         <v>393477618059</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F31" s="1">
         <v>1111</v>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>5</v>
@@ -1818,7 +1818,7 @@
         <v>393477618059</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F32" s="1">
         <v>1111</v>
@@ -1826,10 +1826,10 @@
     </row>
     <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>5</v>
@@ -1838,7 +1838,7 @@
         <v>393477618059</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F33" s="1">
         <v>1111</v>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>5</v>
@@ -1858,7 +1858,7 @@
         <v>393477618059</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F34" s="1">
         <v>1111</v>
@@ -1866,10 +1866,10 @@
     </row>
     <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>5</v>
@@ -1878,7 +1878,7 @@
         <v>393477618059</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F35" s="1">
         <v>1111</v>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>5</v>
@@ -1898,7 +1898,7 @@
         <v>393477618059</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="F36" s="1">
         <v>1111</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>5</v>
@@ -1918,7 +1918,7 @@
         <v>393477618059</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="F37" s="1">
         <v>1111</v>
@@ -1926,10 +1926,10 @@
     </row>
     <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>6</v>
@@ -1938,7 +1938,7 @@
         <v>393516843447</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F38" s="1">
         <v>1234</v>
@@ -1946,10 +1946,10 @@
     </row>
     <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>6</v>
@@ -1958,7 +1958,7 @@
         <v>393382798808</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F39" s="1">
         <v>1234</v>
@@ -1966,10 +1966,10 @@
     </row>
     <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>6</v>
@@ -1978,7 +1978,7 @@
         <v>393477618059</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F40" s="1">
         <v>1111</v>
@@ -1986,10 +1986,10 @@
     </row>
     <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>6</v>
@@ -1998,7 +1998,7 @@
         <v>393477618059</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F41" s="1">
         <v>1111</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>6</v>
@@ -2018,7 +2018,7 @@
         <v>393477618059</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F42" s="1">
         <v>1111</v>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>6</v>
@@ -2038,7 +2038,7 @@
         <v>393477618059</v>
       </c>
       <c r="E43" s="21" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F43" s="1">
         <v>1111</v>
@@ -2049,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>6</v>
@@ -2066,10 +2066,10 @@
     </row>
     <row r="45" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>6</v>
@@ -2078,7 +2078,7 @@
         <v>393477618059</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F45" s="1">
         <v>1111</v>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="46" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>6</v>
@@ -2098,7 +2098,7 @@
         <v>393477618059</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F46" s="1">
         <v>1111</v>
@@ -2106,13 +2106,13 @@
     </row>
     <row r="47" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D47" s="2">
         <v>393477618059</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F47" s="1">
         <v>1111</v>
@@ -2120,10 +2120,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D48" s="2">
         <v>393926352302</v>
@@ -2134,10 +2134,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D49" s="4">
         <v>393475623576</v>
@@ -2148,10 +2148,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D50" s="4">
         <v>393515994998</v>
@@ -2162,16 +2162,16 @@
     </row>
     <row r="51" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="F51" s="1">
         <v>1111</v>
@@ -2179,16 +2179,16 @@
     </row>
     <row r="52" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="17" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="F52" s="1">
         <v>1111</v>
@@ -2196,16 +2196,16 @@
     </row>
     <row r="53" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="17" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F53" s="1">
         <v>1111</v>
@@ -2213,16 +2213,16 @@
     </row>
     <row r="54" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E54" s="16" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="F54" s="1">
         <v>1111</v>
@@ -2230,16 +2230,16 @@
     </row>
     <row r="55" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="17" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E55" s="19" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="F55" s="1">
         <v>1111</v>
@@ -2247,16 +2247,16 @@
     </row>
     <row r="56" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F56" s="1">
         <v>1111</v>
@@ -2264,16 +2264,16 @@
     </row>
     <row r="57" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="17" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="F57" s="1">
         <v>1111</v>
@@ -2281,16 +2281,16 @@
     </row>
     <row r="58" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F58" s="1">
         <v>1111</v>
@@ -2298,16 +2298,16 @@
     </row>
     <row r="59" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C59" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="E59" s="13" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F59" s="1">
         <v>1111</v>
@@ -2315,16 +2315,16 @@
     </row>
     <row r="60" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="15" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F60" s="1">
         <v>1111</v>
@@ -2332,16 +2332,16 @@
     </row>
     <row r="61" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="17" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="F61" s="1">
         <v>1111</v>
@@ -2349,16 +2349,16 @@
     </row>
     <row r="62" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="F62" s="1">
         <v>1111</v>
@@ -2366,16 +2366,16 @@
     </row>
     <row r="63" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="F63" s="1">
         <v>1111</v>
@@ -2383,16 +2383,16 @@
     </row>
     <row r="64" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="13" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="F64" s="1">
         <v>1111</v>
@@ -2400,16 +2400,16 @@
     </row>
     <row r="65" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="13" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F65" s="1">
         <v>1111</v>
@@ -2417,16 +2417,16 @@
     </row>
     <row r="66" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="13" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="F66" s="1">
         <v>1111</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="67" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="13" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="F67" s="1">
         <v>1111</v>
@@ -2451,16 +2451,16 @@
     </row>
     <row r="68" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="15" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F68" s="1">
         <v>1111</v>
@@ -2468,16 +2468,16 @@
     </row>
     <row r="69" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="13" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="F69" s="1">
         <v>1111</v>
@@ -2485,16 +2485,16 @@
     </row>
     <row r="70" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="15" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="F70" s="1">
         <v>1111</v>
@@ -2502,16 +2502,16 @@
     </row>
     <row r="71" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>160</v>
-      </c>
       <c r="E71" s="17" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="F71" s="1">
         <v>1111</v>
@@ -2519,16 +2519,16 @@
     </row>
     <row r="72" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="17" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E72" s="19" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="F72" s="1">
         <v>1111</v>
@@ -2536,16 +2536,16 @@
     </row>
     <row r="73" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="16" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E73" s="18" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F73" s="1">
         <v>1111</v>
@@ -2553,16 +2553,16 @@
     </row>
     <row r="74" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="15" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="F74" s="1">
         <v>1111</v>
@@ -2570,16 +2570,16 @@
     </row>
     <row r="75" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="13" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="F75" s="1">
         <v>1111</v>
@@ -2587,16 +2587,16 @@
     </row>
     <row r="76" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="13" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="F76" s="1">
         <v>1111</v>
@@ -2604,16 +2604,16 @@
     </row>
     <row r="77" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="16" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="E77" s="16" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="F77" s="1">
         <v>1111</v>
@@ -2621,16 +2621,16 @@
     </row>
     <row r="78" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="13" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="F78" s="1">
         <v>1111</v>
@@ -2638,16 +2638,16 @@
     </row>
     <row r="79" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="15" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F79" s="1">
         <v>1111</v>
@@ -2655,16 +2655,16 @@
     </row>
     <row r="80" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="16" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="E80" s="18" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="F80" s="1">
         <v>1111</v>
@@ -2672,16 +2672,16 @@
     </row>
     <row r="81" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="F81" s="1">
         <v>1111</v>
@@ -2689,16 +2689,16 @@
     </row>
     <row r="82" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="13" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="E82" s="16" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="F82" s="1">
         <v>1111</v>
@@ -2706,16 +2706,16 @@
     </row>
     <row r="83" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="17" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="E83" s="18" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="F83" s="1">
         <v>1111</v>
@@ -2723,16 +2723,16 @@
     </row>
     <row r="84" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="E84" s="13" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F84" s="1">
         <v>1111</v>
@@ -2740,16 +2740,16 @@
     </row>
     <row r="85" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="17" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="E85" s="19" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="F85" s="1">
         <v>1111</v>
@@ -2757,16 +2757,16 @@
     </row>
     <row r="86" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="15" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="E86" s="16" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="F86" s="1">
         <v>1111</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="87" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="13" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="F87" s="1">
         <v>1111</v>
@@ -2791,19 +2791,19 @@
     </row>
     <row r="88" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="13" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D88" s="2">
         <v>393297735084</v>
       </c>
       <c r="E88" s="16" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="F88" s="1">
         <v>1111</v>
@@ -2811,19 +2811,19 @@
     </row>
     <row r="89" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="13" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D89" s="2">
         <v>393281527839</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="F89" s="1">
         <v>1111</v>
@@ -2831,19 +2831,19 @@
     </row>
     <row r="90" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="17" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D90" s="2">
         <v>393337039626</v>
       </c>
       <c r="E90" s="17" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="F90" s="1">
         <v>1111</v>
@@ -2851,19 +2851,19 @@
     </row>
     <row r="91" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D91" s="2">
         <v>393668993714</v>
       </c>
       <c r="E91" s="17" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="F91" s="1">
         <v>1111</v>
@@ -2871,19 +2871,19 @@
     </row>
     <row r="92" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="13" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D92" s="2">
         <v>393273997950</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="F92" s="1">
         <v>1111</v>
@@ -2891,19 +2891,19 @@
     </row>
     <row r="93" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="13" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D93" s="2">
         <v>393316298506</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="F93" s="1">
         <v>1111</v>
@@ -2911,19 +2911,19 @@
     </row>
     <row r="94" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="13" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D94" s="2">
         <v>393343140500</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="F94" s="1">
         <v>1111</v>
@@ -2931,19 +2931,19 @@
     </row>
     <row r="95" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="13" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D95" s="2">
         <v>393351612468</v>
       </c>
       <c r="E95" s="16" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="F95" s="1">
         <v>1111</v>
@@ -2951,19 +2951,19 @@
     </row>
     <row r="96" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>212</v>
       </c>
       <c r="D96" s="2">
         <v>393402901672</v>
       </c>
       <c r="E96" s="15" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="F96" s="1">
         <v>1111</v>
@@ -2971,19 +2971,19 @@
     </row>
     <row r="97" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="15" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D97" s="2">
         <v>393510837400</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="F97" s="1">
         <v>1111</v>
@@ -2991,19 +2991,19 @@
     </row>
     <row r="98" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="13" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D98" s="2">
         <v>393421215671</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="F98" s="1">
         <v>1111</v>
@@ -3011,19 +3011,19 @@
     </row>
     <row r="99" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="13" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D99" s="2">
         <v>393313969976</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="F99" s="1">
         <v>1111</v>
@@ -3031,17 +3031,17 @@
     </row>
     <row r="100" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" s="13" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="F100" s="1">
         <v>1111</v>
@@ -3049,17 +3049,17 @@
     </row>
     <row r="101" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="13" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" s="13" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="F101" s="1">
         <v>1111</v>
@@ -3067,17 +3067,17 @@
     </row>
     <row r="102" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="13" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" s="13" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F102" s="1">
         <v>1111</v>
@@ -3085,17 +3085,17 @@
     </row>
     <row r="103" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="16" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" s="18" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="F103" s="1">
         <v>1111</v>
@@ -3103,17 +3103,17 @@
     </row>
     <row r="104" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="13" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" s="13" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="F104" s="1">
         <v>1111</v>
@@ -3121,17 +3121,17 @@
     </row>
     <row r="105" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="13" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" s="13" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="F105" s="1">
         <v>1111</v>
@@ -3139,17 +3139,17 @@
     </row>
     <row r="106" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="15" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" s="15" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="F106" s="1">
         <v>1111</v>
@@ -3157,17 +3157,17 @@
     </row>
     <row r="107" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="13" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" s="13" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="F107" s="1">
         <v>1111</v>
@@ -3175,17 +3175,17 @@
     </row>
     <row r="108" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C108" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>237</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" s="13" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F108" s="1">
         <v>1111</v>
@@ -3193,17 +3193,17 @@
     </row>
     <row r="109" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="20" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" s="20" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="F109" s="1">
         <v>1111</v>
@@ -3211,17 +3211,17 @@
     </row>
     <row r="110" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="15" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" s="13" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="F110" s="1">
         <v>1111</v>
@@ -3229,17 +3229,17 @@
     </row>
     <row r="111" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="15" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" s="13" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="F111" s="1">
         <v>1111</v>

--- a/operatori.xlsx
+++ b/operatori.xlsx
@@ -47,6 +47,9 @@
     <t>Squadra prog. 5 H24</t>
   </si>
   <si>
+    <t>Lettieri Alessandro</t>
+  </si>
+  <si>
     <t>sitav231</t>
   </si>
   <si>
@@ -74,6 +77,9 @@
     <t>elar626</t>
   </si>
   <si>
+    <t>Sibilio Raffaele</t>
+  </si>
+  <si>
     <t>sitav8125</t>
   </si>
   <si>
@@ -131,6 +137,9 @@
     <t>sitav1149</t>
   </si>
   <si>
+    <t>Bellezza Pasquale</t>
+  </si>
+  <si>
     <t>sitav8003</t>
   </si>
   <si>
@@ -152,6 +161,9 @@
     <t>sitav8185</t>
   </si>
   <si>
+    <t>Fontemagi Fabio</t>
+  </si>
+  <si>
     <t>sitav8041</t>
   </si>
   <si>
@@ -173,6 +185,9 @@
     <t>sitav8329</t>
   </si>
   <si>
+    <t>Manzo Giovanni</t>
+  </si>
+  <si>
     <t>elar6131</t>
   </si>
   <si>
@@ -200,6 +215,9 @@
     <t>sitav8225</t>
   </si>
   <si>
+    <t>Marrazzo Pietro</t>
+  </si>
+  <si>
     <t>sitav8264</t>
   </si>
   <si>
@@ -221,6 +239,9 @@
     <t>sitav8224</t>
   </si>
   <si>
+    <t>Panico Daniele</t>
+  </si>
+  <si>
     <t>sitav8263</t>
   </si>
   <si>
@@ -260,6 +281,9 @@
     <t>elar6249</t>
   </si>
   <si>
+    <t>Guerriero Vincenzo</t>
+  </si>
+  <si>
     <t>sitav1136</t>
   </si>
   <si>
@@ -714,30 +738,6 @@
   </si>
   <si>
     <t>Squadra corr. 5 H24</t>
-  </si>
-  <si>
-    <t>lettieri</t>
-  </si>
-  <si>
-    <t>sibilio</t>
-  </si>
-  <si>
-    <t>bellezza</t>
-  </si>
-  <si>
-    <t>fontemagi</t>
-  </si>
-  <si>
-    <t>manzo</t>
-  </si>
-  <si>
-    <t>marrazzo</t>
-  </si>
-  <si>
-    <t>panico</t>
-  </si>
-  <si>
-    <t>guerriero</t>
   </si>
 </sst>
 </file>
@@ -1186,30 +1186,30 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>230</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
@@ -1218,7 +1218,7 @@
         <v>393457186030</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1">
         <v>1234</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2</v>
@@ -1238,7 +1238,7 @@
         <v>393477748517</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F3" s="1">
         <v>1111</v>
@@ -1246,10 +1246,10 @@
     </row>
     <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>232</v>
+        <v>37</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>2</v>
@@ -1258,7 +1258,7 @@
         <v>393338751617</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F4" s="1">
         <v>1111</v>
@@ -1266,10 +1266,10 @@
     </row>
     <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>233</v>
+        <v>45</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>2</v>
@@ -1278,7 +1278,7 @@
         <v>393472634487</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F5" s="1">
         <v>1111</v>
@@ -1286,10 +1286,10 @@
     </row>
     <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>234</v>
+        <v>53</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>2</v>
@@ -1298,7 +1298,7 @@
         <v>393477618059</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F6" s="1">
         <v>1111</v>
@@ -1306,10 +1306,10 @@
     </row>
     <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>235</v>
+        <v>63</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>2</v>
@@ -1318,7 +1318,7 @@
         <v>393388867929</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F7" s="1">
         <v>1111</v>
@@ -1326,10 +1326,10 @@
     </row>
     <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>236</v>
+        <v>71</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>2</v>
@@ -1338,7 +1338,7 @@
         <v>393924426156</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F8" s="1">
         <v>1111</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>237</v>
+        <v>85</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>2</v>
@@ -1358,7 +1358,7 @@
         <v>393477618059</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F9" s="1">
         <v>1111</v>
@@ -1366,10 +1366,10 @@
     </row>
     <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -1378,7 +1378,7 @@
         <v>393312365048</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10" s="1">
         <v>1234</v>
@@ -1386,10 +1386,10 @@
     </row>
     <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1398,7 +1398,7 @@
         <v>393381449666</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F11" s="1">
         <v>1111</v>
@@ -1406,10 +1406,10 @@
     </row>
     <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1418,7 +1418,7 @@
         <v>393294285283</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F12" s="1">
         <v>1234</v>
@@ -1426,10 +1426,10 @@
     </row>
     <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1438,7 +1438,7 @@
         <v>393348446091</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F13" s="1">
         <v>1111</v>
@@ -1446,10 +1446,10 @@
     </row>
     <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1458,7 +1458,7 @@
         <v>393477618059</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F14" s="1">
         <v>1111</v>
@@ -1466,10 +1466,10 @@
     </row>
     <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -1478,7 +1478,7 @@
         <v>393349016062</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F15" s="1">
         <v>1111</v>
@@ -1486,10 +1486,10 @@
     </row>
     <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1498,7 +1498,7 @@
         <v>393477618059</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F16" s="1">
         <v>1111</v>
@@ -1506,10 +1506,10 @@
     </row>
     <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1518,7 +1518,7 @@
         <v>393477618059</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F17" s="1">
         <v>1111</v>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1538,7 +1538,7 @@
         <v>393477618059</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F18" s="1">
         <v>1111</v>
@@ -1546,10 +1546,10 @@
     </row>
     <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>4</v>
@@ -1558,7 +1558,7 @@
         <v>393477618059</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F19" s="1">
         <v>1234</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>4</v>
@@ -1578,7 +1578,7 @@
         <v>393477618059</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F20" s="1">
         <v>1234</v>
@@ -1586,10 +1586,10 @@
     </row>
     <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>4</v>
@@ -1598,7 +1598,7 @@
         <v>393477618059</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F21" s="1">
         <v>1111</v>
@@ -1606,10 +1606,10 @@
     </row>
     <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>4</v>
@@ -1618,7 +1618,7 @@
         <v>393477618059</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F22" s="1">
         <v>1111</v>
@@ -1626,10 +1626,10 @@
     </row>
     <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>4</v>
@@ -1638,7 +1638,7 @@
         <v>393477618059</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F23" s="1">
         <v>1111</v>
@@ -1646,10 +1646,10 @@
     </row>
     <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>4</v>
@@ -1658,7 +1658,7 @@
         <v>393477618059</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F24" s="1">
         <v>1111</v>
@@ -1666,10 +1666,10 @@
     </row>
     <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>4</v>
@@ -1678,7 +1678,7 @@
         <v>393477618059</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F25" s="1">
         <v>1111</v>
@@ -1686,10 +1686,10 @@
     </row>
     <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>4</v>
@@ -1698,7 +1698,7 @@
         <v>393477618059</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F26" s="1">
         <v>1111</v>
@@ -1706,10 +1706,10 @@
     </row>
     <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>4</v>
@@ -1718,7 +1718,7 @@
         <v>393477618059</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F27" s="1">
         <v>1111</v>
@@ -1726,10 +1726,10 @@
     </row>
     <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>5</v>
@@ -1738,7 +1738,7 @@
         <v>393477618059</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F28" s="1">
         <v>1234</v>
@@ -1746,10 +1746,10 @@
     </row>
     <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>5</v>
@@ -1758,7 +1758,7 @@
         <v>393477618059</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F29" s="1">
         <v>1234</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>5</v>
@@ -1778,7 +1778,7 @@
         <v>393477618059</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F30" s="1">
         <v>1111</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>5</v>
@@ -1798,7 +1798,7 @@
         <v>393477618059</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F31" s="1">
         <v>1111</v>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>5</v>
@@ -1818,7 +1818,7 @@
         <v>393477618059</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F32" s="1">
         <v>1111</v>
@@ -1826,10 +1826,10 @@
     </row>
     <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>5</v>
@@ -1838,7 +1838,7 @@
         <v>393477618059</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F33" s="1">
         <v>1111</v>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>5</v>
@@ -1858,7 +1858,7 @@
         <v>393477618059</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F34" s="1">
         <v>1111</v>
@@ -1866,10 +1866,10 @@
     </row>
     <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>5</v>
@@ -1878,7 +1878,7 @@
         <v>393477618059</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F35" s="1">
         <v>1111</v>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>5</v>
@@ -1898,7 +1898,7 @@
         <v>393477618059</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F36" s="1">
         <v>1111</v>
@@ -1906,10 +1906,10 @@
     </row>
     <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>5</v>
@@ -1918,7 +1918,7 @@
         <v>393477618059</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F37" s="1">
         <v>1111</v>
@@ -1926,10 +1926,10 @@
     </row>
     <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>6</v>
@@ -1938,7 +1938,7 @@
         <v>393516843447</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F38" s="1">
         <v>1234</v>
@@ -1946,10 +1946,10 @@
     </row>
     <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>6</v>
@@ -1958,7 +1958,7 @@
         <v>393382798808</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F39" s="1">
         <v>1234</v>
@@ -1966,10 +1966,10 @@
     </row>
     <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>6</v>
@@ -1978,7 +1978,7 @@
         <v>393477618059</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F40" s="1">
         <v>1111</v>
@@ -1986,10 +1986,10 @@
     </row>
     <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>6</v>
@@ -1998,7 +1998,7 @@
         <v>393477618059</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F41" s="1">
         <v>1111</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>6</v>
@@ -2018,7 +2018,7 @@
         <v>393477618059</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F42" s="1">
         <v>1111</v>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>6</v>
@@ -2038,7 +2038,7 @@
         <v>393477618059</v>
       </c>
       <c r="E43" s="21" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F43" s="1">
         <v>1111</v>
@@ -2049,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>6</v>
@@ -2066,10 +2066,10 @@
     </row>
     <row r="45" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>6</v>
@@ -2078,7 +2078,7 @@
         <v>393477618059</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="F45" s="1">
         <v>1111</v>
@@ -2086,10 +2086,10 @@
     </row>
     <row r="46" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>6</v>
@@ -2098,7 +2098,7 @@
         <v>393477618059</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F46" s="1">
         <v>1111</v>
@@ -2106,13 +2106,13 @@
     </row>
     <row r="47" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D47" s="2">
         <v>393477618059</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F47" s="1">
         <v>1111</v>
@@ -2120,10 +2120,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="D48" s="2">
         <v>393926352302</v>
@@ -2134,10 +2134,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D49" s="4">
         <v>393475623576</v>
@@ -2148,10 +2148,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="D50" s="4">
         <v>393515994998</v>
@@ -2162,16 +2162,16 @@
     </row>
     <row r="51" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="F51" s="1">
         <v>1111</v>
@@ -2179,16 +2179,16 @@
     </row>
     <row r="52" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="B52" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B52" s="5" t="s">
-        <v>97</v>
-      </c>
       <c r="C52" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="F52" s="1">
         <v>1111</v>
@@ -2196,16 +2196,16 @@
     </row>
     <row r="53" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="17" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="F53" s="1">
         <v>1111</v>
@@ -2213,16 +2213,16 @@
     </row>
     <row r="54" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E54" s="16" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="F54" s="1">
         <v>1111</v>
@@ -2230,16 +2230,16 @@
     </row>
     <row r="55" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="17" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E55" s="19" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F55" s="1">
         <v>1111</v>
@@ -2247,16 +2247,16 @@
     </row>
     <row r="56" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F56" s="1">
         <v>1111</v>
@@ -2264,16 +2264,16 @@
     </row>
     <row r="57" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="17" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="F57" s="1">
         <v>1111</v>
@@ -2281,16 +2281,16 @@
     </row>
     <row r="58" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="F58" s="1">
         <v>1111</v>
@@ -2298,16 +2298,16 @@
     </row>
     <row r="59" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="F59" s="1">
         <v>1111</v>
@@ -2315,16 +2315,16 @@
     </row>
     <row r="60" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="15" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="F60" s="1">
         <v>1111</v>
@@ -2332,16 +2332,16 @@
     </row>
     <row r="61" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="17" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="F61" s="1">
         <v>1111</v>
@@ -2349,16 +2349,16 @@
     </row>
     <row r="62" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="13" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="F62" s="1">
         <v>1111</v>
@@ -2366,16 +2366,16 @@
     </row>
     <row r="63" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="F63" s="1">
         <v>1111</v>
@@ -2383,16 +2383,16 @@
     </row>
     <row r="64" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="13" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="F64" s="1">
         <v>1111</v>
@@ -2400,16 +2400,16 @@
     </row>
     <row r="65" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="13" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="F65" s="1">
         <v>1111</v>
@@ -2417,16 +2417,16 @@
     </row>
     <row r="66" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="13" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F66" s="1">
         <v>1111</v>
@@ -2434,16 +2434,16 @@
     </row>
     <row r="67" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="13" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="F67" s="1">
         <v>1111</v>
@@ -2451,16 +2451,16 @@
     </row>
     <row r="68" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="15" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="F68" s="1">
         <v>1111</v>
@@ -2468,16 +2468,16 @@
     </row>
     <row r="69" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="13" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F69" s="1">
         <v>1111</v>
@@ -2485,16 +2485,16 @@
     </row>
     <row r="70" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="15" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="F70" s="1">
         <v>1111</v>
@@ -2502,16 +2502,16 @@
     </row>
     <row r="71" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E71" s="17" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="F71" s="1">
         <v>1111</v>
@@ -2519,16 +2519,16 @@
     </row>
     <row r="72" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="17" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E72" s="19" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="F72" s="1">
         <v>1111</v>
@@ -2536,16 +2536,16 @@
     </row>
     <row r="73" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="16" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E73" s="18" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="F73" s="1">
         <v>1111</v>
@@ -2553,16 +2553,16 @@
     </row>
     <row r="74" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="15" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="F74" s="1">
         <v>1111</v>
@@ -2570,16 +2570,16 @@
     </row>
     <row r="75" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="13" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="F75" s="1">
         <v>1111</v>
@@ -2587,16 +2587,16 @@
     </row>
     <row r="76" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="13" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="F76" s="1">
         <v>1111</v>
@@ -2604,16 +2604,16 @@
     </row>
     <row r="77" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="16" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="E77" s="16" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="F77" s="1">
         <v>1111</v>
@@ -2621,16 +2621,16 @@
     </row>
     <row r="78" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="13" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F78" s="1">
         <v>1111</v>
@@ -2638,16 +2638,16 @@
     </row>
     <row r="79" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="15" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="F79" s="1">
         <v>1111</v>
@@ -2655,16 +2655,16 @@
     </row>
     <row r="80" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="16" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="E80" s="18" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="F80" s="1">
         <v>1111</v>
@@ -2672,16 +2672,16 @@
     </row>
     <row r="81" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="F81" s="1">
         <v>1111</v>
@@ -2689,16 +2689,16 @@
     </row>
     <row r="82" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="13" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="E82" s="16" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F82" s="1">
         <v>1111</v>
@@ -2706,16 +2706,16 @@
     </row>
     <row r="83" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="17" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="E83" s="18" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="F83" s="1">
         <v>1111</v>
@@ -2723,16 +2723,16 @@
     </row>
     <row r="84" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="15" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="F84" s="1">
         <v>1111</v>
@@ -2740,16 +2740,16 @@
     </row>
     <row r="85" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="17" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="E85" s="19" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="F85" s="1">
         <v>1111</v>
@@ -2757,16 +2757,16 @@
     </row>
     <row r="86" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="15" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="E86" s="16" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="F86" s="1">
         <v>1111</v>
@@ -2774,16 +2774,16 @@
     </row>
     <row r="87" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="13" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="F87" s="1">
         <v>1111</v>
@@ -2791,19 +2791,19 @@
     </row>
     <row r="88" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="13" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D88" s="2">
         <v>393297735084</v>
       </c>
       <c r="E88" s="16" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="F88" s="1">
         <v>1111</v>
@@ -2811,19 +2811,19 @@
     </row>
     <row r="89" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="13" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D89" s="2">
         <v>393281527839</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="F89" s="1">
         <v>1111</v>
@@ -2831,19 +2831,19 @@
     </row>
     <row r="90" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="17" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D90" s="2">
         <v>393337039626</v>
       </c>
       <c r="E90" s="17" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="F90" s="1">
         <v>1111</v>
@@ -2851,19 +2851,19 @@
     </row>
     <row r="91" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D91" s="2">
         <v>393668993714</v>
       </c>
       <c r="E91" s="17" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="F91" s="1">
         <v>1111</v>
@@ -2871,19 +2871,19 @@
     </row>
     <row r="92" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="13" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D92" s="2">
         <v>393273997950</v>
       </c>
       <c r="E92" s="13" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="F92" s="1">
         <v>1111</v>
@@ -2891,19 +2891,19 @@
     </row>
     <row r="93" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="13" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D93" s="2">
         <v>393316298506</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="F93" s="1">
         <v>1111</v>
@@ -2911,19 +2911,19 @@
     </row>
     <row r="94" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="13" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D94" s="2">
         <v>393343140500</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F94" s="1">
         <v>1111</v>
@@ -2931,19 +2931,19 @@
     </row>
     <row r="95" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="13" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D95" s="2">
         <v>393351612468</v>
       </c>
       <c r="E95" s="16" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="F95" s="1">
         <v>1111</v>
@@ -2951,19 +2951,19 @@
     </row>
     <row r="96" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="15" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D96" s="2">
         <v>393402901672</v>
       </c>
       <c r="E96" s="15" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="F96" s="1">
         <v>1111</v>
@@ -2971,19 +2971,19 @@
     </row>
     <row r="97" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="15" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D97" s="2">
         <v>393510837400</v>
       </c>
       <c r="E97" s="13" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="F97" s="1">
         <v>1111</v>
@@ -2991,19 +2991,19 @@
     </row>
     <row r="98" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="13" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D98" s="2">
         <v>393421215671</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="F98" s="1">
         <v>1111</v>
@@ -3011,19 +3011,19 @@
     </row>
     <row r="99" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="13" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D99" s="2">
         <v>393313969976</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="F99" s="1">
         <v>1111</v>
@@ -3031,17 +3031,17 @@
     </row>
     <row r="100" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" s="13" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="F100" s="1">
         <v>1111</v>
@@ -3049,17 +3049,17 @@
     </row>
     <row r="101" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="13" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" s="13" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="F101" s="1">
         <v>1111</v>
@@ -3067,17 +3067,17 @@
     </row>
     <row r="102" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="13" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" s="13" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="F102" s="1">
         <v>1111</v>
@@ -3085,17 +3085,17 @@
     </row>
     <row r="103" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="16" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" s="18" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="F103" s="1">
         <v>1111</v>
@@ -3103,17 +3103,17 @@
     </row>
     <row r="104" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="13" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" s="13" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="F104" s="1">
         <v>1111</v>
@@ -3121,17 +3121,17 @@
     </row>
     <row r="105" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="13" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" s="13" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="F105" s="1">
         <v>1111</v>
@@ -3139,17 +3139,17 @@
     </row>
     <row r="106" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="15" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" s="15" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="F106" s="1">
         <v>1111</v>
@@ -3157,17 +3157,17 @@
     </row>
     <row r="107" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="13" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" s="13" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="F107" s="1">
         <v>1111</v>
@@ -3175,17 +3175,17 @@
     </row>
     <row r="108" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="13" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" s="13" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="F108" s="1">
         <v>1111</v>
@@ -3193,17 +3193,17 @@
     </row>
     <row r="109" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="20" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" s="20" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="F109" s="1">
         <v>1111</v>
@@ -3211,17 +3211,17 @@
     </row>
     <row r="110" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="15" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" s="13" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="F110" s="1">
         <v>1111</v>
@@ -3229,17 +3229,17 @@
     </row>
     <row r="111" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="15" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" s="13" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F111" s="1">
         <v>1111</v>

--- a/operatori.xlsx
+++ b/operatori.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="241">
   <si>
     <t>Borriello Pasquale</t>
   </si>
@@ -738,6 +738,15 @@
   </si>
   <si>
     <t>Squadra corr. 5 H24</t>
+  </si>
+  <si>
+    <t>Morello Daniele</t>
+  </si>
+  <si>
+    <t>Ingegneria</t>
+  </si>
+  <si>
+    <t>Cacace Riccardo</t>
   </si>
 </sst>
 </file>
@@ -1173,7 +1182,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F123"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.42578125" style="6" bestFit="1" customWidth="1"/>
@@ -2108,6 +2117,12 @@
       <c r="A47" s="8" t="s">
         <v>107</v>
       </c>
+      <c r="B47" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>239</v>
+      </c>
       <c r="D47" s="2">
         <v>393477618059</v>
       </c>
@@ -2115,114 +2130,125 @@
         <v>98</v>
       </c>
       <c r="F47" s="1">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>108</v>
+        <v>240</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>102</v>
+        <v>239</v>
       </c>
       <c r="D48" s="2">
-        <v>393926352302</v>
-      </c>
+        <v>393663708135</v>
+      </c>
+      <c r="E48" s="13"/>
       <c r="F48" s="1">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>110</v>
+        <v>238</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D49" s="4">
-        <v>393475623576</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="D49" s="2">
+        <v>393280937356</v>
+      </c>
+      <c r="E49" s="13"/>
       <c r="F49" s="1">
-        <v>1111</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D50" s="4">
-        <v>393515994998</v>
+        <v>102</v>
+      </c>
+      <c r="D50" s="2">
+        <v>393926352302</v>
       </c>
       <c r="F50" s="1">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="13" t="s">
-        <v>111</v>
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="8" t="s">
+        <v>110</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>105</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>112</v>
+        <v>100</v>
+      </c>
+      <c r="D51" s="4">
+        <v>393475623576</v>
       </c>
       <c r="F51" s="1">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="17" t="s">
-        <v>113</v>
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="8" t="s">
+        <v>109</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>105</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E52" s="17" t="s">
-        <v>114</v>
+        <v>101</v>
+      </c>
+      <c r="D52" s="4">
+        <v>393515994998</v>
       </c>
       <c r="F52" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>106</v>
+      <c r="A53" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E53" s="19" t="s">
-        <v>116</v>
+      <c r="E53" s="13" t="s">
+        <v>112</v>
       </c>
       <c r="F53" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>106</v>
+      <c r="A54" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E54" s="16" t="s">
-        <v>118</v>
+      <c r="E54" s="17" t="s">
+        <v>114</v>
       </c>
       <c r="F54" s="1">
         <v>1111</v>
@@ -2230,7 +2256,7 @@
     </row>
     <row r="55" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="17" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>106</v>
@@ -2239,15 +2265,15 @@
         <v>135</v>
       </c>
       <c r="E55" s="19" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F55" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="13" t="s">
-        <v>121</v>
+      <c r="A56" s="16" t="s">
+        <v>117</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>106</v>
@@ -2255,8 +2281,8 @@
       <c r="C56" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E56" s="13" t="s">
-        <v>122</v>
+      <c r="E56" s="16" t="s">
+        <v>118</v>
       </c>
       <c r="F56" s="1">
         <v>1111</v>
@@ -2264,7 +2290,7 @@
     </row>
     <row r="57" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>106</v>
@@ -2273,15 +2299,15 @@
         <v>135</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F57" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="15" t="s">
-        <v>125</v>
+      <c r="A58" s="13" t="s">
+        <v>121</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>106</v>
@@ -2290,15 +2316,15 @@
         <v>135</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F58" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="13" t="s">
-        <v>127</v>
+      <c r="A59" s="17" t="s">
+        <v>123</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>106</v>
@@ -2306,8 +2332,8 @@
       <c r="C59" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E59" s="13" t="s">
-        <v>128</v>
+      <c r="E59" s="19" t="s">
+        <v>124</v>
       </c>
       <c r="F59" s="1">
         <v>1111</v>
@@ -2315,7 +2341,7 @@
     </row>
     <row r="60" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="15" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>106</v>
@@ -2324,15 +2350,15 @@
         <v>135</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F60" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="17" t="s">
-        <v>131</v>
+      <c r="A61" s="13" t="s">
+        <v>127</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>106</v>
@@ -2341,15 +2367,15 @@
         <v>135</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F61" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="13" t="s">
-        <v>133</v>
+      <c r="A62" s="15" t="s">
+        <v>129</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>106</v>
@@ -2358,7 +2384,7 @@
         <v>135</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F62" s="1">
         <v>1111</v>
@@ -2366,16 +2392,16 @@
     </row>
     <row r="63" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E63" s="17" t="s">
-        <v>137</v>
+        <v>135</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>132</v>
       </c>
       <c r="F63" s="1">
         <v>1111</v>
@@ -2383,33 +2409,33 @@
     </row>
     <row r="64" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="13" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E64" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="F64" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A65" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E64" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="F64" s="1">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E65" s="16" t="s">
-        <v>141</v>
+      <c r="E65" s="17" t="s">
+        <v>137</v>
       </c>
       <c r="F65" s="1">
         <v>1111</v>
@@ -2417,16 +2443,16 @@
     </row>
     <row r="66" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="13" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>160</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F66" s="1">
         <v>1111</v>
@@ -2434,7 +2460,7 @@
     </row>
     <row r="67" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="13" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>106</v>
@@ -2442,16 +2468,16 @@
       <c r="C67" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E67" s="13" t="s">
-        <v>145</v>
+      <c r="E67" s="16" t="s">
+        <v>141</v>
       </c>
       <c r="F67" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A68" s="15" t="s">
-        <v>146</v>
+      <c r="A68" s="13" t="s">
+        <v>142</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>106</v>
@@ -2459,8 +2485,8 @@
       <c r="C68" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E68" s="15" t="s">
-        <v>147</v>
+      <c r="E68" s="13" t="s">
+        <v>143</v>
       </c>
       <c r="F68" s="1">
         <v>1111</v>
@@ -2468,7 +2494,7 @@
     </row>
     <row r="69" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="13" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>106</v>
@@ -2477,7 +2503,7 @@
         <v>160</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F69" s="1">
         <v>1111</v>
@@ -2485,7 +2511,7 @@
     </row>
     <row r="70" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="15" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>106</v>
@@ -2493,16 +2519,16 @@
       <c r="C70" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E70" s="13" t="s">
-        <v>151</v>
+      <c r="E70" s="15" t="s">
+        <v>147</v>
       </c>
       <c r="F70" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A71" s="17" t="s">
-        <v>152</v>
+      <c r="A71" s="13" t="s">
+        <v>148</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>106</v>
@@ -2510,16 +2536,16 @@
       <c r="C71" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E71" s="17" t="s">
-        <v>153</v>
+      <c r="E71" s="13" t="s">
+        <v>149</v>
       </c>
       <c r="F71" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A72" s="17" t="s">
-        <v>154</v>
+      <c r="A72" s="15" t="s">
+        <v>150</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>106</v>
@@ -2527,16 +2553,16 @@
       <c r="C72" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E72" s="19" t="s">
-        <v>155</v>
+      <c r="E72" s="13" t="s">
+        <v>151</v>
       </c>
       <c r="F72" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="16" t="s">
-        <v>156</v>
+      <c r="A73" s="17" t="s">
+        <v>152</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>106</v>
@@ -2544,16 +2570,16 @@
       <c r="C73" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E73" s="18" t="s">
-        <v>157</v>
+      <c r="E73" s="17" t="s">
+        <v>153</v>
       </c>
       <c r="F73" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="15" t="s">
-        <v>158</v>
+      <c r="A74" s="17" t="s">
+        <v>154</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>106</v>
@@ -2561,59 +2587,59 @@
       <c r="C74" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E74" s="13" t="s">
+      <c r="E74" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="F74" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A75" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E75" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="F75" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A76" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E76" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="F74" s="1">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A75" s="13" t="s">
+      <c r="F76" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A77" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B77" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E75" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="F75" s="1">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E76" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="F76" s="1">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A77" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E77" s="16" t="s">
-        <v>166</v>
+      <c r="E77" s="13" t="s">
+        <v>162</v>
       </c>
       <c r="F77" s="1">
         <v>1111</v>
@@ -2621,7 +2647,7 @@
     </row>
     <row r="78" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="13" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>106</v>
@@ -2630,15 +2656,15 @@
         <v>187</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F78" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="15" t="s">
-        <v>169</v>
+      <c r="A79" s="16" t="s">
+        <v>165</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>106</v>
@@ -2646,16 +2672,16 @@
       <c r="C79" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E79" s="15" t="s">
-        <v>170</v>
+      <c r="E79" s="16" t="s">
+        <v>166</v>
       </c>
       <c r="F79" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="16" t="s">
-        <v>171</v>
+      <c r="A80" s="13" t="s">
+        <v>167</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>106</v>
@@ -2663,16 +2689,16 @@
       <c r="C80" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E80" s="18" t="s">
-        <v>172</v>
+      <c r="E80" s="13" t="s">
+        <v>168</v>
       </c>
       <c r="F80" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A81" s="13" t="s">
-        <v>173</v>
+      <c r="A81" s="15" t="s">
+        <v>169</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>106</v>
@@ -2680,16 +2706,16 @@
       <c r="C81" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E81" s="13" t="s">
-        <v>174</v>
+      <c r="E81" s="15" t="s">
+        <v>170</v>
       </c>
       <c r="F81" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A82" s="13" t="s">
-        <v>175</v>
+      <c r="A82" s="16" t="s">
+        <v>171</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>106</v>
@@ -2697,33 +2723,33 @@
       <c r="C82" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E82" s="16" t="s">
-        <v>176</v>
+      <c r="E82" s="18" t="s">
+        <v>172</v>
       </c>
       <c r="F82" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A83" s="17" t="s">
-        <v>177</v>
+      <c r="A83" s="13" t="s">
+        <v>173</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E83" s="18" t="s">
-        <v>178</v>
+      <c r="E83" s="13" t="s">
+        <v>174</v>
       </c>
       <c r="F83" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A84" s="15" t="s">
-        <v>179</v>
+      <c r="A84" s="13" t="s">
+        <v>175</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>106</v>
@@ -2731,8 +2757,8 @@
       <c r="C84" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E84" s="13" t="s">
-        <v>180</v>
+      <c r="E84" s="16" t="s">
+        <v>176</v>
       </c>
       <c r="F84" s="1">
         <v>1111</v>
@@ -2740,16 +2766,16 @@
     </row>
     <row r="85" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="17" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E85" s="19" t="s">
-        <v>182</v>
+      <c r="E85" s="18" t="s">
+        <v>178</v>
       </c>
       <c r="F85" s="1">
         <v>1111</v>
@@ -2757,7 +2783,7 @@
     </row>
     <row r="86" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="15" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>106</v>
@@ -2765,16 +2791,16 @@
       <c r="C86" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E86" s="16" t="s">
-        <v>184</v>
+      <c r="E86" s="13" t="s">
+        <v>180</v>
       </c>
       <c r="F86" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A87" s="13" t="s">
-        <v>185</v>
+      <c r="A87" s="17" t="s">
+        <v>181</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>106</v>
@@ -2782,28 +2808,25 @@
       <c r="C87" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E87" s="13" t="s">
-        <v>186</v>
+      <c r="E87" s="19" t="s">
+        <v>182</v>
       </c>
       <c r="F87" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A88" s="13" t="s">
-        <v>188</v>
+      <c r="A88" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D88" s="2">
-        <v>393297735084</v>
+        <v>187</v>
       </c>
       <c r="E88" s="16" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="F88" s="1">
         <v>1111</v>
@@ -2811,67 +2834,64 @@
     </row>
     <row r="89" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="13" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B89" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E89" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="F89" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A90" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D89" s="2">
-        <v>393281527839</v>
-      </c>
-      <c r="E89" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="F89" s="1">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A90" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>212</v>
       </c>
       <c r="D90" s="2">
-        <v>393337039626</v>
-      </c>
-      <c r="E90" s="17" t="s">
-        <v>193</v>
+        <v>393297735084</v>
+      </c>
+      <c r="E90" s="16" t="s">
+        <v>189</v>
       </c>
       <c r="F90" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A91" s="17" t="s">
-        <v>194</v>
+      <c r="A91" s="13" t="s">
+        <v>190</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>212</v>
       </c>
       <c r="D91" s="2">
-        <v>393668993714</v>
-      </c>
-      <c r="E91" s="17" t="s">
-        <v>195</v>
+        <v>393281527839</v>
+      </c>
+      <c r="E91" s="13" t="s">
+        <v>191</v>
       </c>
       <c r="F91" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" s="13" t="s">
-        <v>196</v>
+      <c r="A92" s="17" t="s">
+        <v>192</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>106</v>
@@ -2880,18 +2900,18 @@
         <v>212</v>
       </c>
       <c r="D92" s="2">
-        <v>393273997950</v>
-      </c>
-      <c r="E92" s="13" t="s">
-        <v>197</v>
+        <v>393337039626</v>
+      </c>
+      <c r="E92" s="17" t="s">
+        <v>193</v>
       </c>
       <c r="F92" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="13" t="s">
-        <v>198</v>
+      <c r="A93" s="17" t="s">
+        <v>194</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>106</v>
@@ -2900,10 +2920,10 @@
         <v>212</v>
       </c>
       <c r="D93" s="2">
-        <v>393316298506</v>
-      </c>
-      <c r="E93" s="13" t="s">
-        <v>199</v>
+        <v>393668993714</v>
+      </c>
+      <c r="E93" s="17" t="s">
+        <v>195</v>
       </c>
       <c r="F93" s="1">
         <v>1111</v>
@@ -2911,7 +2931,7 @@
     </row>
     <row r="94" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="13" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>106</v>
@@ -2920,10 +2940,10 @@
         <v>212</v>
       </c>
       <c r="D94" s="2">
-        <v>393343140500</v>
+        <v>393273997950</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F94" s="1">
         <v>1111</v>
@@ -2931,7 +2951,7 @@
     </row>
     <row r="95" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>106</v>
@@ -2940,18 +2960,18 @@
         <v>212</v>
       </c>
       <c r="D95" s="2">
-        <v>393351612468</v>
-      </c>
-      <c r="E95" s="16" t="s">
-        <v>203</v>
+        <v>393316298506</v>
+      </c>
+      <c r="E95" s="13" t="s">
+        <v>199</v>
       </c>
       <c r="F95" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A96" s="15" t="s">
-        <v>204</v>
+      <c r="A96" s="13" t="s">
+        <v>200</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>106</v>
@@ -2960,18 +2980,18 @@
         <v>212</v>
       </c>
       <c r="D96" s="2">
-        <v>393402901672</v>
-      </c>
-      <c r="E96" s="15" t="s">
-        <v>205</v>
+        <v>393343140500</v>
+      </c>
+      <c r="E96" s="13" t="s">
+        <v>201</v>
       </c>
       <c r="F96" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A97" s="15" t="s">
-        <v>206</v>
+      <c r="A97" s="13" t="s">
+        <v>202</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>106</v>
@@ -2980,18 +3000,18 @@
         <v>212</v>
       </c>
       <c r="D97" s="2">
-        <v>393510837400</v>
-      </c>
-      <c r="E97" s="13" t="s">
-        <v>207</v>
+        <v>393351612468</v>
+      </c>
+      <c r="E97" s="16" t="s">
+        <v>203</v>
       </c>
       <c r="F97" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A98" s="13" t="s">
-        <v>208</v>
+      <c r="A98" s="15" t="s">
+        <v>204</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>106</v>
@@ -3000,18 +3020,18 @@
         <v>212</v>
       </c>
       <c r="D98" s="2">
-        <v>393421215671</v>
-      </c>
-      <c r="E98" s="13" t="s">
-        <v>209</v>
+        <v>393402901672</v>
+      </c>
+      <c r="E98" s="15" t="s">
+        <v>205</v>
       </c>
       <c r="F98" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A99" s="13" t="s">
-        <v>210</v>
+      <c r="A99" s="15" t="s">
+        <v>206</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>106</v>
@@ -3020,10 +3040,10 @@
         <v>212</v>
       </c>
       <c r="D99" s="2">
-        <v>393313969976</v>
+        <v>393510837400</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F99" s="1">
         <v>1111</v>
@@ -3031,17 +3051,19 @@
     </row>
     <row r="100" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D100" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="D100" s="2">
+        <v>393421215671</v>
+      </c>
       <c r="E100" s="13" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F100" s="1">
         <v>1111</v>
@@ -3049,17 +3071,19 @@
     </row>
     <row r="101" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="13" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D101" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="D101" s="2">
+        <v>393313969976</v>
+      </c>
       <c r="E101" s="13" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F101" s="1">
         <v>1111</v>
@@ -3067,35 +3091,35 @@
     </row>
     <row r="102" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="13" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" s="13" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="F102" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A103" s="16" t="s">
-        <v>219</v>
+      <c r="A103" s="13" t="s">
+        <v>215</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D103" s="2"/>
-      <c r="E103" s="18" t="s">
-        <v>220</v>
+      <c r="E103" s="13" t="s">
+        <v>216</v>
       </c>
       <c r="F103" s="1">
         <v>1111</v>
@@ -3103,7 +3127,7 @@
     </row>
     <row r="104" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="13" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>106</v>
@@ -3113,15 +3137,15 @@
       </c>
       <c r="D104" s="2"/>
       <c r="E104" s="13" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F104" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="13" t="s">
-        <v>223</v>
+      <c r="A105" s="16" t="s">
+        <v>219</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>106</v>
@@ -3130,16 +3154,16 @@
         <v>237</v>
       </c>
       <c r="D105" s="2"/>
-      <c r="E105" s="13" t="s">
-        <v>224</v>
+      <c r="E105" s="18" t="s">
+        <v>220</v>
       </c>
       <c r="F105" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A106" s="15" t="s">
-        <v>225</v>
+      <c r="A106" s="13" t="s">
+        <v>221</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>106</v>
@@ -3148,8 +3172,8 @@
         <v>237</v>
       </c>
       <c r="D106" s="2"/>
-      <c r="E106" s="15" t="s">
-        <v>226</v>
+      <c r="E106" s="13" t="s">
+        <v>222</v>
       </c>
       <c r="F106" s="1">
         <v>1111</v>
@@ -3157,7 +3181,7 @@
     </row>
     <row r="107" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="13" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>106</v>
@@ -3167,15 +3191,15 @@
       </c>
       <c r="D107" s="2"/>
       <c r="E107" s="13" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F107" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A108" s="13" t="s">
-        <v>229</v>
+      <c r="A108" s="15" t="s">
+        <v>225</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>106</v>
@@ -3184,16 +3208,16 @@
         <v>237</v>
       </c>
       <c r="D108" s="2"/>
-      <c r="E108" s="13" t="s">
-        <v>230</v>
+      <c r="E108" s="15" t="s">
+        <v>226</v>
       </c>
       <c r="F108" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A109" s="20" t="s">
-        <v>231</v>
+      <c r="A109" s="13" t="s">
+        <v>227</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>106</v>
@@ -3202,16 +3226,16 @@
         <v>237</v>
       </c>
       <c r="D109" s="2"/>
-      <c r="E109" s="20" t="s">
-        <v>232</v>
+      <c r="E109" s="13" t="s">
+        <v>228</v>
       </c>
       <c r="F109" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A110" s="15" t="s">
-        <v>233</v>
+      <c r="A110" s="13" t="s">
+        <v>229</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>106</v>
@@ -3221,15 +3245,15 @@
       </c>
       <c r="D110" s="2"/>
       <c r="E110" s="13" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F110" s="1">
         <v>1111</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A111" s="15" t="s">
-        <v>235</v>
+      <c r="A111" s="20" t="s">
+        <v>231</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>106</v>
@@ -3238,48 +3262,84 @@
         <v>237</v>
       </c>
       <c r="D111" s="2"/>
-      <c r="E111" s="13" t="s">
+      <c r="E111" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="F111" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A112" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D112" s="2"/>
+      <c r="E112" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="F112" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A113" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D113" s="2"/>
+      <c r="E113" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="F111" s="1">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D112" s="2"/>
-    </row>
-    <row r="113" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D113" s="2"/>
-    </row>
-    <row r="114" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="F113" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D114" s="2"/>
     </row>
-    <row r="115" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D115" s="2"/>
     </row>
-    <row r="116" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D116" s="2"/>
     </row>
-    <row r="117" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D117" s="2"/>
     </row>
-    <row r="118" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D118" s="2"/>
     </row>
-    <row r="119" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D119" s="2"/>
     </row>
-    <row r="120" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D120" s="2"/>
     </row>
-    <row r="121" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D121" s="2"/>
     </row>
-    <row r="122" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D122" s="2"/>
     </row>
-    <row r="123" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D123" s="2"/>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D124" s="2"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D125" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/operatori.xlsx
+++ b/operatori.xlsx
@@ -1182,13 +1182,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.42578125" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" style="12" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
@@ -1203,7 +1203,7 @@
       <c r="C1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>99</v>
       </c>
       <c r="E1" s="12" t="s">
@@ -1303,8 +1303,8 @@
       <c r="C6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="3">
-        <v>393477618059</v>
+      <c r="D6" s="4">
+        <v>393355772910</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>54</v>
@@ -2230,6 +2230,9 @@
       <c r="C53" s="1" t="s">
         <v>135</v>
       </c>
+      <c r="D53" s="2">
+        <v>393515021820</v>
+      </c>
       <c r="E53" s="13" t="s">
         <v>112</v>
       </c>
@@ -2247,6 +2250,9 @@
       <c r="C54" s="1" t="s">
         <v>135</v>
       </c>
+      <c r="D54" s="2">
+        <v>393452888506</v>
+      </c>
       <c r="E54" s="17" t="s">
         <v>114</v>
       </c>
@@ -2264,6 +2270,9 @@
       <c r="C55" s="1" t="s">
         <v>135</v>
       </c>
+      <c r="D55" s="2">
+        <v>393493529625</v>
+      </c>
       <c r="E55" s="19" t="s">
         <v>116</v>
       </c>
@@ -2281,6 +2290,9 @@
       <c r="C56" s="1" t="s">
         <v>135</v>
       </c>
+      <c r="D56" s="2">
+        <v>393277080530</v>
+      </c>
       <c r="E56" s="16" t="s">
         <v>118</v>
       </c>
@@ -3099,7 +3111,6 @@
       <c r="C102" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D102" s="2"/>
       <c r="E102" s="13" t="s">
         <v>214</v>
       </c>
@@ -3117,7 +3128,6 @@
       <c r="C103" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D103" s="2"/>
       <c r="E103" s="13" t="s">
         <v>216</v>
       </c>
@@ -3135,7 +3145,6 @@
       <c r="C104" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D104" s="2"/>
       <c r="E104" s="13" t="s">
         <v>218</v>
       </c>
@@ -3153,7 +3162,6 @@
       <c r="C105" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D105" s="2"/>
       <c r="E105" s="18" t="s">
         <v>220</v>
       </c>
@@ -3171,7 +3179,6 @@
       <c r="C106" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D106" s="2"/>
       <c r="E106" s="13" t="s">
         <v>222</v>
       </c>
@@ -3189,7 +3196,6 @@
       <c r="C107" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D107" s="2"/>
       <c r="E107" s="13" t="s">
         <v>224</v>
       </c>
@@ -3207,7 +3213,6 @@
       <c r="C108" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D108" s="2"/>
       <c r="E108" s="15" t="s">
         <v>226</v>
       </c>
@@ -3225,7 +3230,6 @@
       <c r="C109" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D109" s="2"/>
       <c r="E109" s="13" t="s">
         <v>228</v>
       </c>
@@ -3243,7 +3247,6 @@
       <c r="C110" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D110" s="2"/>
       <c r="E110" s="13" t="s">
         <v>230</v>
       </c>
@@ -3261,7 +3264,6 @@
       <c r="C111" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D111" s="2"/>
       <c r="E111" s="20" t="s">
         <v>232</v>
       </c>
@@ -3279,7 +3281,6 @@
       <c r="C112" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D112" s="2"/>
       <c r="E112" s="13" t="s">
         <v>234</v>
       </c>
@@ -3297,49 +3298,12 @@
       <c r="C113" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D113" s="2"/>
       <c r="E113" s="13" t="s">
         <v>236</v>
       </c>
       <c r="F113" s="1">
         <v>1111</v>
       </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D114" s="2"/>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D115" s="2"/>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D116" s="2"/>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D117" s="2"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D118" s="2"/>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D119" s="2"/>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D120" s="2"/>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D121" s="2"/>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D122" s="2"/>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D123" s="2"/>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D124" s="2"/>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D125" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/operatori.xlsx
+++ b/operatori.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="242">
   <si>
     <t>Borriello Pasquale</t>
   </si>
@@ -747,6 +747,9 @@
   </si>
   <si>
     <t>Cacace Riccardo</t>
+  </si>
+  <si>
+    <t>Grimaldi Daniele</t>
   </si>
 </sst>
 </file>
@@ -1182,7 +1185,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F113"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.42578125" style="6" bestFit="1" customWidth="1"/>
@@ -1503,9 +1506,6 @@
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D16" s="2">
-        <v>393477618059</v>
-      </c>
       <c r="E16" s="13" t="s">
         <v>88</v>
       </c>
@@ -1523,9 +1523,6 @@
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D17" s="2">
-        <v>393477618059</v>
-      </c>
       <c r="E17" s="13" t="s">
         <v>80</v>
       </c>
@@ -1543,9 +1540,6 @@
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="2">
-        <v>393477618059</v>
-      </c>
       <c r="E18" s="13" t="s">
         <v>76</v>
       </c>
@@ -1563,9 +1557,6 @@
       <c r="C19" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D19" s="2">
-        <v>393477618059</v>
-      </c>
       <c r="E19" s="17" t="s">
         <v>12</v>
       </c>
@@ -1583,9 +1574,6 @@
       <c r="C20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D20" s="2">
-        <v>393477618059</v>
-      </c>
       <c r="E20" s="13" t="s">
         <v>22</v>
       </c>
@@ -1603,9 +1591,6 @@
       <c r="C21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="2">
-        <v>393477618059</v>
-      </c>
       <c r="E21" s="13" t="s">
         <v>32</v>
       </c>
@@ -1623,9 +1608,6 @@
       <c r="C22" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="2">
-        <v>393477618059</v>
-      </c>
       <c r="E22" s="18" t="s">
         <v>70</v>
       </c>
@@ -1643,9 +1625,6 @@
       <c r="C23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D23" s="2">
-        <v>393477618059</v>
-      </c>
       <c r="E23" s="16" t="s">
         <v>58</v>
       </c>
@@ -1663,9 +1642,6 @@
       <c r="C24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D24" s="2">
-        <v>393477618059</v>
-      </c>
       <c r="E24" s="15" t="s">
         <v>66</v>
       </c>
@@ -1684,7 +1660,7 @@
         <v>4</v>
       </c>
       <c r="D25" s="2">
-        <v>393477618059</v>
+        <v>393349751201</v>
       </c>
       <c r="E25" s="13" t="s">
         <v>28</v>
@@ -1703,9 +1679,6 @@
       <c r="C26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D26" s="2">
-        <v>393477618059</v>
-      </c>
       <c r="E26" s="13" t="s">
         <v>92</v>
       </c>
@@ -1723,9 +1696,6 @@
       <c r="C27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D27" s="2">
-        <v>393477618059</v>
-      </c>
       <c r="E27" s="13" t="s">
         <v>81</v>
       </c>
@@ -1744,7 +1714,7 @@
         <v>5</v>
       </c>
       <c r="D28" s="2">
-        <v>393477618059</v>
+        <v>393338613354</v>
       </c>
       <c r="E28" s="19" t="s">
         <v>14</v>
@@ -1763,9 +1733,6 @@
       <c r="C29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D29" s="2">
-        <v>393477618059</v>
-      </c>
       <c r="E29" s="20" t="s">
         <v>24</v>
       </c>
@@ -1783,9 +1750,6 @@
       <c r="C30" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D30" s="2">
-        <v>393477618059</v>
-      </c>
       <c r="E30" s="13" t="s">
         <v>42</v>
       </c>
@@ -1803,9 +1767,6 @@
       <c r="C31" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D31" s="2">
-        <v>393477618059</v>
-      </c>
       <c r="E31" s="15" t="s">
         <v>50</v>
       </c>
@@ -1823,9 +1784,6 @@
       <c r="C32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D32" s="2">
-        <v>393477618059</v>
-      </c>
       <c r="E32" s="16" t="s">
         <v>34</v>
       </c>
@@ -1843,9 +1801,6 @@
       <c r="C33" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D33" s="2">
-        <v>393477618059</v>
-      </c>
       <c r="E33" s="15" t="s">
         <v>60</v>
       </c>
@@ -1863,9 +1818,6 @@
       <c r="C34" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D34" s="2">
-        <v>393477618059</v>
-      </c>
       <c r="E34" s="15" t="s">
         <v>68</v>
       </c>
@@ -1883,9 +1835,6 @@
       <c r="C35" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D35" s="2">
-        <v>393477618059</v>
-      </c>
       <c r="E35" s="13" t="s">
         <v>90</v>
       </c>
@@ -1903,9 +1852,6 @@
       <c r="C36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D36" s="2">
-        <v>393477618059</v>
-      </c>
       <c r="E36" s="15" t="s">
         <v>73</v>
       </c>
@@ -1923,9 +1869,6 @@
       <c r="C37" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D37" s="2">
-        <v>393477618059</v>
-      </c>
       <c r="E37" s="13" t="s">
         <v>84</v>
       </c>
@@ -3302,6 +3245,23 @@
         <v>236</v>
       </c>
       <c r="F113" s="1">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D114" s="2">
+        <v>393662816645</v>
+      </c>
+      <c r="F114" s="1">
         <v>1111</v>
       </c>
     </row>

--- a/operatori.xlsx
+++ b/operatori.xlsx
@@ -452,9 +452,6 @@
     <t>sitav1153</t>
   </si>
   <si>
-    <t>Esposito Antonio 73</t>
-  </si>
-  <si>
     <t>sitav1161</t>
   </si>
   <si>
@@ -750,6 +747,9 @@
   </si>
   <si>
     <t>Grimaldi Daniele</t>
+  </si>
+  <si>
+    <t>Esposito Antonio</t>
   </si>
 </sst>
 </file>
@@ -2064,7 +2064,7 @@
         <v>105</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D47" s="2">
         <v>393477618059</v>
@@ -2078,13 +2078,13 @@
     </row>
     <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>105</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D48" s="2">
         <v>393663708135</v>
@@ -2096,13 +2096,13 @@
     </row>
     <row r="49" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>105</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D49" s="2">
         <v>393280937356</v>
@@ -2387,7 +2387,7 @@
         <v>105</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E65" s="17" t="s">
         <v>137</v>
@@ -2404,7 +2404,7 @@
         <v>105</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E66" s="13" t="s">
         <v>139</v>
@@ -2421,7 +2421,10 @@
         <v>106</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
+      </c>
+      <c r="D67" s="2">
+        <v>393249025348</v>
       </c>
       <c r="E67" s="16" t="s">
         <v>141</v>
@@ -2432,16 +2435,19 @@
     </row>
     <row r="68" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D68" s="2">
+        <v>393476870641</v>
+      </c>
+      <c r="E68" s="13" t="s">
         <v>142</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E68" s="13" t="s">
-        <v>143</v>
       </c>
       <c r="F68" s="1">
         <v>1111</v>
@@ -2449,16 +2455,16 @@
     </row>
     <row r="69" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E69" s="13" t="s">
         <v>144</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E69" s="13" t="s">
-        <v>145</v>
       </c>
       <c r="F69" s="1">
         <v>1111</v>
@@ -2466,16 +2472,16 @@
     </row>
     <row r="70" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E70" s="15" t="s">
         <v>146</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E70" s="15" t="s">
-        <v>147</v>
       </c>
       <c r="F70" s="1">
         <v>1111</v>
@@ -2483,16 +2489,16 @@
     </row>
     <row r="71" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E71" s="13" t="s">
         <v>148</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E71" s="13" t="s">
-        <v>149</v>
       </c>
       <c r="F71" s="1">
         <v>1111</v>
@@ -2500,16 +2506,16 @@
     </row>
     <row r="72" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E72" s="13" t="s">
         <v>150</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E72" s="13" t="s">
-        <v>151</v>
       </c>
       <c r="F72" s="1">
         <v>1111</v>
@@ -2517,16 +2523,16 @@
     </row>
     <row r="73" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E73" s="17" t="s">
         <v>152</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E73" s="17" t="s">
-        <v>153</v>
       </c>
       <c r="F73" s="1">
         <v>1111</v>
@@ -2534,16 +2540,16 @@
     </row>
     <row r="74" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E74" s="19" t="s">
         <v>154</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E74" s="19" t="s">
-        <v>155</v>
       </c>
       <c r="F74" s="1">
         <v>1111</v>
@@ -2551,16 +2557,16 @@
     </row>
     <row r="75" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E75" s="18" t="s">
         <v>156</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E75" s="18" t="s">
-        <v>157</v>
       </c>
       <c r="F75" s="1">
         <v>1111</v>
@@ -2568,16 +2574,16 @@
     </row>
     <row r="76" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E76" s="13" t="s">
         <v>158</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E76" s="13" t="s">
-        <v>159</v>
       </c>
       <c r="F76" s="1">
         <v>1111</v>
@@ -2585,16 +2591,16 @@
     </row>
     <row r="77" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>105</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F77" s="1">
         <v>1111</v>
@@ -2602,16 +2608,16 @@
     </row>
     <row r="78" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E78" s="13" t="s">
         <v>163</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E78" s="13" t="s">
-        <v>164</v>
       </c>
       <c r="F78" s="1">
         <v>1111</v>
@@ -2619,16 +2625,16 @@
     </row>
     <row r="79" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E79" s="16" t="s">
         <v>165</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E79" s="16" t="s">
-        <v>166</v>
       </c>
       <c r="F79" s="1">
         <v>1111</v>
@@ -2636,16 +2642,16 @@
     </row>
     <row r="80" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E80" s="13" t="s">
         <v>167</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E80" s="13" t="s">
-        <v>168</v>
       </c>
       <c r="F80" s="1">
         <v>1111</v>
@@ -2653,16 +2659,16 @@
     </row>
     <row r="81" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E81" s="15" t="s">
         <v>169</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E81" s="15" t="s">
-        <v>170</v>
       </c>
       <c r="F81" s="1">
         <v>1111</v>
@@ -2670,16 +2676,16 @@
     </row>
     <row r="82" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E82" s="18" t="s">
         <v>171</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E82" s="18" t="s">
-        <v>172</v>
       </c>
       <c r="F82" s="1">
         <v>1111</v>
@@ -2687,16 +2693,16 @@
     </row>
     <row r="83" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E83" s="13" t="s">
         <v>173</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E83" s="13" t="s">
-        <v>174</v>
       </c>
       <c r="F83" s="1">
         <v>1111</v>
@@ -2704,16 +2710,16 @@
     </row>
     <row r="84" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E84" s="16" t="s">
         <v>175</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E84" s="16" t="s">
-        <v>176</v>
       </c>
       <c r="F84" s="1">
         <v>1111</v>
@@ -2721,16 +2727,16 @@
     </row>
     <row r="85" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>105</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E85" s="18" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F85" s="1">
         <v>1111</v>
@@ -2738,16 +2744,16 @@
     </row>
     <row r="86" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E86" s="13" t="s">
         <v>179</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E86" s="13" t="s">
-        <v>180</v>
       </c>
       <c r="F86" s="1">
         <v>1111</v>
@@ -2755,16 +2761,16 @@
     </row>
     <row r="87" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E87" s="19" t="s">
         <v>181</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E87" s="19" t="s">
-        <v>182</v>
       </c>
       <c r="F87" s="1">
         <v>1111</v>
@@ -2772,16 +2778,16 @@
     </row>
     <row r="88" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E88" s="16" t="s">
         <v>183</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E88" s="16" t="s">
-        <v>184</v>
       </c>
       <c r="F88" s="1">
         <v>1111</v>
@@ -2789,16 +2795,16 @@
     </row>
     <row r="89" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E89" s="13" t="s">
         <v>185</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E89" s="13" t="s">
-        <v>186</v>
       </c>
       <c r="F89" s="1">
         <v>1111</v>
@@ -2806,19 +2812,19 @@
     </row>
     <row r="90" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>105</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D90" s="2">
         <v>393297735084</v>
       </c>
       <c r="E90" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F90" s="1">
         <v>1111</v>
@@ -2826,19 +2832,19 @@
     </row>
     <row r="91" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>105</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D91" s="2">
         <v>393281527839</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F91" s="1">
         <v>1111</v>
@@ -2846,19 +2852,19 @@
     </row>
     <row r="92" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="17" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D92" s="2">
         <v>393337039626</v>
       </c>
       <c r="E92" s="17" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F92" s="1">
         <v>1111</v>
@@ -2866,19 +2872,19 @@
     </row>
     <row r="93" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D93" s="2">
         <v>393668993714</v>
       </c>
       <c r="E93" s="17" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F93" s="1">
         <v>1111</v>
@@ -2886,19 +2892,19 @@
     </row>
     <row r="94" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D94" s="2">
         <v>393273997950</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F94" s="1">
         <v>1111</v>
@@ -2906,19 +2912,19 @@
     </row>
     <row r="95" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D95" s="2">
         <v>393316298506</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F95" s="1">
         <v>1111</v>
@@ -2926,19 +2932,19 @@
     </row>
     <row r="96" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D96" s="2">
         <v>393343140500</v>
       </c>
       <c r="E96" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F96" s="1">
         <v>1111</v>
@@ -2946,19 +2952,19 @@
     </row>
     <row r="97" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D97" s="2">
         <v>393351612468</v>
       </c>
       <c r="E97" s="16" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F97" s="1">
         <v>1111</v>
@@ -2966,19 +2972,19 @@
     </row>
     <row r="98" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D98" s="2">
         <v>393402901672</v>
       </c>
       <c r="E98" s="15" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F98" s="1">
         <v>1111</v>
@@ -2986,19 +2992,19 @@
     </row>
     <row r="99" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="15" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D99" s="2">
         <v>393510837400</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F99" s="1">
         <v>1111</v>
@@ -3006,19 +3012,19 @@
     </row>
     <row r="100" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D100" s="2">
         <v>393421215671</v>
       </c>
       <c r="E100" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F100" s="1">
         <v>1111</v>
@@ -3026,19 +3032,19 @@
     </row>
     <row r="101" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>106</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D101" s="2">
         <v>393313969976</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F101" s="1">
         <v>1111</v>
@@ -3046,16 +3052,16 @@
     </row>
     <row r="102" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>105</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F102" s="1">
         <v>1111</v>
@@ -3063,16 +3069,16 @@
     </row>
     <row r="103" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>105</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F103" s="1">
         <v>1111</v>
@@ -3080,16 +3086,16 @@
     </row>
     <row r="104" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E104" s="13" t="s">
         <v>217</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E104" s="13" t="s">
-        <v>218</v>
       </c>
       <c r="F104" s="1">
         <v>1111</v>
@@ -3097,16 +3103,16 @@
     </row>
     <row r="105" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E105" s="18" t="s">
         <v>219</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E105" s="18" t="s">
-        <v>220</v>
       </c>
       <c r="F105" s="1">
         <v>1111</v>
@@ -3114,16 +3120,16 @@
     </row>
     <row r="106" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E106" s="13" t="s">
         <v>221</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E106" s="13" t="s">
-        <v>222</v>
       </c>
       <c r="F106" s="1">
         <v>1111</v>
@@ -3131,16 +3137,16 @@
     </row>
     <row r="107" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E107" s="13" t="s">
         <v>223</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E107" s="13" t="s">
-        <v>224</v>
       </c>
       <c r="F107" s="1">
         <v>1111</v>
@@ -3148,16 +3154,16 @@
     </row>
     <row r="108" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E108" s="15" t="s">
         <v>225</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E108" s="15" t="s">
-        <v>226</v>
       </c>
       <c r="F108" s="1">
         <v>1111</v>
@@ -3165,16 +3171,16 @@
     </row>
     <row r="109" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E109" s="13" t="s">
         <v>227</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E109" s="13" t="s">
-        <v>228</v>
       </c>
       <c r="F109" s="1">
         <v>1111</v>
@@ -3182,16 +3188,16 @@
     </row>
     <row r="110" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E110" s="13" t="s">
         <v>229</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E110" s="13" t="s">
-        <v>230</v>
       </c>
       <c r="F110" s="1">
         <v>1111</v>
@@ -3199,16 +3205,16 @@
     </row>
     <row r="111" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E111" s="20" t="s">
         <v>231</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E111" s="20" t="s">
-        <v>232</v>
       </c>
       <c r="F111" s="1">
         <v>1111</v>
@@ -3216,16 +3222,16 @@
     </row>
     <row r="112" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E112" s="13" t="s">
         <v>233</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E112" s="13" t="s">
-        <v>234</v>
       </c>
       <c r="F112" s="1">
         <v>1111</v>
@@ -3233,16 +3239,16 @@
     </row>
     <row r="113" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E113" s="13" t="s">
         <v>235</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E113" s="13" t="s">
-        <v>236</v>
       </c>
       <c r="F113" s="1">
         <v>1111</v>
@@ -3250,7 +3256,7 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>106</v>

--- a/operatori.xlsx
+++ b/operatori.xlsx
@@ -795,7 +795,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -805,12 +805,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -848,11 +842,10 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1188,16 +1181,16 @@
   <dimension ref="A1:F114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.42578125" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>96</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1209,7 +1202,7 @@
       <c r="D1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>97</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -1217,7 +1210,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1229,7 +1222,7 @@
       <c r="D2" s="2">
         <v>393457186030</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="12" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="1">
@@ -1237,7 +1230,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1249,15 +1242,15 @@
       <c r="D3" s="2">
         <v>393477748517</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="13" t="s">
         <v>18</v>
       </c>
       <c r="F3" s="1">
-        <v>1111</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1269,7 +1262,7 @@
       <c r="D4" s="2">
         <v>393338751617</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="12" t="s">
         <v>38</v>
       </c>
       <c r="F4" s="1">
@@ -1277,7 +1270,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>45</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1289,7 +1282,7 @@
       <c r="D5" s="2">
         <v>393472634487</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="12" t="s">
         <v>46</v>
       </c>
       <c r="F5" s="1">
@@ -1297,7 +1290,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>53</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -1306,10 +1299,10 @@
       <c r="C6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>393355772910</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="12" t="s">
         <v>54</v>
       </c>
       <c r="F6" s="1">
@@ -1317,7 +1310,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>63</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -1329,7 +1322,7 @@
       <c r="D7" s="2">
         <v>393388867929</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="14" t="s">
         <v>64</v>
       </c>
       <c r="F7" s="1">
@@ -1337,7 +1330,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>71</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -1349,7 +1342,7 @@
       <c r="D8" s="2">
         <v>393924426156</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="12" t="s">
         <v>72</v>
       </c>
       <c r="F8" s="1">
@@ -1357,7 +1350,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>85</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -1369,7 +1362,7 @@
       <c r="D9" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="12" t="s">
         <v>86</v>
       </c>
       <c r="F9" s="1">
@@ -1377,7 +1370,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -1389,7 +1382,7 @@
       <c r="D10" s="2">
         <v>393312365048</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="12" t="s">
         <v>10</v>
       </c>
       <c r="F10" s="1">
@@ -1397,7 +1390,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -1409,7 +1402,7 @@
       <c r="D11" s="2">
         <v>393381449666</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="15" t="s">
         <v>20</v>
       </c>
       <c r="F11" s="1">
@@ -1417,7 +1410,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>29</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -1429,7 +1422,7 @@
       <c r="D12" s="2">
         <v>393294285283</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="14" t="s">
         <v>30</v>
       </c>
       <c r="F12" s="1">
@@ -1437,7 +1430,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>39</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -1449,7 +1442,7 @@
       <c r="D13" s="2">
         <v>393348446091</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="12" t="s">
         <v>40</v>
       </c>
       <c r="F13" s="1">
@@ -1457,7 +1450,7 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -1466,10 +1459,8 @@
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="3">
-        <v>393477618059</v>
-      </c>
-      <c r="E14" s="17" t="s">
+      <c r="D14" s="3"/>
+      <c r="E14" s="16" t="s">
         <v>48</v>
       </c>
       <c r="F14" s="1">
@@ -1477,7 +1468,7 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>55</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -1489,7 +1480,7 @@
       <c r="D15" s="2">
         <v>393349016062</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="14" t="s">
         <v>56</v>
       </c>
       <c r="F15" s="1">
@@ -1497,7 +1488,7 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>87</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -1506,7 +1497,7 @@
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="12" t="s">
         <v>88</v>
       </c>
       <c r="F16" s="1">
@@ -1514,7 +1505,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>77</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -1523,7 +1514,7 @@
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="12" t="s">
         <v>80</v>
       </c>
       <c r="F17" s="1">
@@ -1531,7 +1522,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="9" t="s">
         <v>75</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -1540,7 +1531,7 @@
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F18" s="1">
@@ -1548,7 +1539,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="8" t="s">
         <v>11</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -1557,7 +1548,7 @@
       <c r="C19" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F19" s="1">
@@ -1565,7 +1556,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -1574,7 +1565,7 @@
       <c r="C20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="12" t="s">
         <v>22</v>
       </c>
       <c r="F20" s="1">
@@ -1582,7 +1573,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>31</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -1591,7 +1582,7 @@
       <c r="C21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="12" t="s">
         <v>32</v>
       </c>
       <c r="F21" s="1">
@@ -1599,7 +1590,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="8" t="s">
         <v>69</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -1608,7 +1599,7 @@
       <c r="C22" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="17" t="s">
         <v>70</v>
       </c>
       <c r="F22" s="1">
@@ -1616,7 +1607,7 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="8" t="s">
         <v>57</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -1625,7 +1616,7 @@
       <c r="C23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E23" s="16" t="s">
+      <c r="E23" s="15" t="s">
         <v>58</v>
       </c>
       <c r="F23" s="1">
@@ -1633,7 +1624,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>65</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -1642,7 +1633,7 @@
       <c r="C24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="14" t="s">
         <v>66</v>
       </c>
       <c r="F24" s="1">
@@ -1650,7 +1641,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="6" t="s">
         <v>27</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -1662,7 +1653,7 @@
       <c r="D25" s="2">
         <v>393349751201</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="E25" s="12" t="s">
         <v>28</v>
       </c>
       <c r="F25" s="1">
@@ -1670,7 +1661,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="7" t="s">
         <v>91</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -1679,7 +1670,7 @@
       <c r="C26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E26" s="13" t="s">
+      <c r="E26" s="12" t="s">
         <v>92</v>
       </c>
       <c r="F26" s="1">
@@ -1687,7 +1678,7 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="7" t="s">
         <v>78</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -1696,7 +1687,7 @@
       <c r="C27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E27" s="13" t="s">
+      <c r="E27" s="12" t="s">
         <v>81</v>
       </c>
       <c r="F27" s="1">
@@ -1704,7 +1695,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -1716,7 +1707,7 @@
       <c r="D28" s="2">
         <v>393338613354</v>
       </c>
-      <c r="E28" s="19" t="s">
+      <c r="E28" s="18" t="s">
         <v>14</v>
       </c>
       <c r="F28" s="1">
@@ -1724,7 +1715,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="10" t="s">
         <v>23</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -1733,7 +1724,7 @@
       <c r="C29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E29" s="20" t="s">
+      <c r="E29" s="19" t="s">
         <v>24</v>
       </c>
       <c r="F29" s="1">
@@ -1741,7 +1732,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="6" t="s">
         <v>41</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -1750,7 +1741,7 @@
       <c r="C30" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="13" t="s">
+      <c r="E30" s="12" t="s">
         <v>42</v>
       </c>
       <c r="F30" s="1">
@@ -1758,7 +1749,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="7" t="s">
         <v>49</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -1767,7 +1758,7 @@
       <c r="C31" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E31" s="15" t="s">
+      <c r="E31" s="14" t="s">
         <v>50</v>
       </c>
       <c r="F31" s="1">
@@ -1775,7 +1766,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -1784,7 +1775,7 @@
       <c r="C32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E32" s="16" t="s">
+      <c r="E32" s="15" t="s">
         <v>34</v>
       </c>
       <c r="F32" s="1">
@@ -1792,7 +1783,7 @@
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="7" t="s">
         <v>59</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -1801,7 +1792,7 @@
       <c r="C33" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E33" s="15" t="s">
+      <c r="E33" s="14" t="s">
         <v>60</v>
       </c>
       <c r="F33" s="1">
@@ -1809,7 +1800,7 @@
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="7" t="s">
         <v>67</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -1818,7 +1809,7 @@
       <c r="C34" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="E34" s="14" t="s">
         <v>68</v>
       </c>
       <c r="F34" s="1">
@@ -1826,7 +1817,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="7" t="s">
         <v>89</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -1835,7 +1826,7 @@
       <c r="C35" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="E35" s="12" t="s">
         <v>90</v>
       </c>
       <c r="F35" s="1">
@@ -1843,7 +1834,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="7" t="s">
         <v>74</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -1852,7 +1843,7 @@
       <c r="C36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E36" s="15" t="s">
+      <c r="E36" s="14" t="s">
         <v>73</v>
       </c>
       <c r="F36" s="1">
@@ -1860,7 +1851,7 @@
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="7" t="s">
         <v>83</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -1869,7 +1860,7 @@
       <c r="C37" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E37" s="13" t="s">
+      <c r="E37" s="12" t="s">
         <v>84</v>
       </c>
       <c r="F37" s="1">
@@ -1877,7 +1868,7 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -1889,7 +1880,7 @@
       <c r="D38" s="2">
         <v>393516843447</v>
       </c>
-      <c r="E38" s="13" t="s">
+      <c r="E38" s="12" t="s">
         <v>16</v>
       </c>
       <c r="F38" s="1">
@@ -1897,7 +1888,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="9" t="s">
+      <c r="A39" s="8" t="s">
         <v>25</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -1909,7 +1900,7 @@
       <c r="D39" s="2">
         <v>393382798808</v>
       </c>
-      <c r="E39" s="16" t="s">
+      <c r="E39" s="15" t="s">
         <v>26</v>
       </c>
       <c r="F39" s="1">
@@ -1917,7 +1908,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="9" t="s">
+      <c r="A40" s="8" t="s">
         <v>35</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -1929,7 +1920,7 @@
       <c r="D40" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E40" s="17" t="s">
+      <c r="E40" s="16" t="s">
         <v>36</v>
       </c>
       <c r="F40" s="1">
@@ -1937,7 +1928,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
+      <c r="A41" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -1949,7 +1940,7 @@
       <c r="D41" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E41" s="13" t="s">
+      <c r="E41" s="12" t="s">
         <v>44</v>
       </c>
       <c r="F41" s="1">
@@ -1957,7 +1948,7 @@
       </c>
     </row>
     <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="9" t="s">
+      <c r="A42" s="8" t="s">
         <v>51</v>
       </c>
       <c r="B42" s="1" t="s">
@@ -1969,7 +1960,7 @@
       <c r="D42" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E42" s="15" t="s">
+      <c r="E42" s="14" t="s">
         <v>52</v>
       </c>
       <c r="F42" s="1">
@@ -1977,7 +1968,7 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="7" t="s">
         <v>61</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -1989,7 +1980,7 @@
       <c r="D43" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E43" s="21" t="s">
+      <c r="E43" s="20" t="s">
         <v>62</v>
       </c>
       <c r="F43" s="1">
@@ -1997,7 +1988,7 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B44" s="1" t="s">
@@ -2009,7 +2000,7 @@
       <c r="D44" s="2">
         <v>393334360904</v>
       </c>
-      <c r="E44" s="13" t="s">
+      <c r="E44" s="12" t="s">
         <v>1</v>
       </c>
       <c r="F44" s="1">
@@ -2017,7 +2008,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="7" t="s">
         <v>93</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -2029,7 +2020,7 @@
       <c r="D45" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E45" s="13" t="s">
+      <c r="E45" s="12" t="s">
         <v>94</v>
       </c>
       <c r="F45" s="1">
@@ -2037,7 +2028,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="7" t="s">
         <v>79</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -2049,7 +2040,7 @@
       <c r="D46" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E46" s="13" t="s">
+      <c r="E46" s="12" t="s">
         <v>82</v>
       </c>
       <c r="F46" s="1">
@@ -2057,10 +2048,10 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="4" t="s">
         <v>105</v>
       </c>
       <c r="C47" s="1" t="s">
@@ -2069,7 +2060,7 @@
       <c r="D47" s="2">
         <v>393477618059</v>
       </c>
-      <c r="E47" s="13" t="s">
+      <c r="E47" s="12" t="s">
         <v>98</v>
       </c>
       <c r="F47" s="1">
@@ -2077,10 +2068,10 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="4" t="s">
         <v>105</v>
       </c>
       <c r="C48" s="1" t="s">
@@ -2089,16 +2080,16 @@
       <c r="D48" s="2">
         <v>393663708135</v>
       </c>
-      <c r="E48" s="13"/>
+      <c r="E48" s="12"/>
       <c r="F48" s="1">
         <v>1234</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="4" t="s">
         <v>105</v>
       </c>
       <c r="C49" s="1" t="s">
@@ -2107,16 +2098,16 @@
       <c r="D49" s="2">
         <v>393280937356</v>
       </c>
-      <c r="E49" s="13"/>
+      <c r="E49" s="12"/>
       <c r="F49" s="1">
         <v>1234</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="4" t="s">
         <v>105</v>
       </c>
       <c r="C50" s="1" t="s">
@@ -2130,16 +2121,16 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="4" t="s">
         <v>105</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D51" s="3">
         <v>393475623576</v>
       </c>
       <c r="F51" s="1">
@@ -2147,16 +2138,16 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="4" t="s">
         <v>105</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D52" s="4">
+      <c r="D52" s="3">
         <v>393515994998</v>
       </c>
       <c r="F52" s="1">
@@ -2164,10 +2155,10 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="13" t="s">
+      <c r="A53" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="4" t="s">
         <v>105</v>
       </c>
       <c r="C53" s="1" t="s">
@@ -2176,18 +2167,18 @@
       <c r="D53" s="2">
         <v>393515021820</v>
       </c>
-      <c r="E53" s="13" t="s">
+      <c r="E53" s="12" t="s">
         <v>112</v>
       </c>
       <c r="F53" s="1">
-        <v>1111</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="17" t="s">
+      <c r="A54" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="4" t="s">
         <v>105</v>
       </c>
       <c r="C54" s="1" t="s">
@@ -2196,15 +2187,15 @@
       <c r="D54" s="2">
         <v>393452888506</v>
       </c>
-      <c r="E54" s="17" t="s">
+      <c r="E54" s="16" t="s">
         <v>114</v>
       </c>
       <c r="F54" s="1">
-        <v>1111</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="17" t="s">
+      <c r="A55" s="16" t="s">
         <v>115</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -2216,7 +2207,7 @@
       <c r="D55" s="2">
         <v>393493529625</v>
       </c>
-      <c r="E55" s="19" t="s">
+      <c r="E55" s="18" t="s">
         <v>116</v>
       </c>
       <c r="F55" s="1">
@@ -2224,7 +2215,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="16" t="s">
+      <c r="A56" s="15" t="s">
         <v>117</v>
       </c>
       <c r="B56" s="1" t="s">
@@ -2236,7 +2227,7 @@
       <c r="D56" s="2">
         <v>393277080530</v>
       </c>
-      <c r="E56" s="16" t="s">
+      <c r="E56" s="15" t="s">
         <v>118</v>
       </c>
       <c r="F56" s="1">
@@ -2244,7 +2235,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="17" t="s">
+      <c r="A57" s="16" t="s">
         <v>119</v>
       </c>
       <c r="B57" s="1" t="s">
@@ -2253,7 +2244,7 @@
       <c r="C57" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E57" s="19" t="s">
+      <c r="E57" s="18" t="s">
         <v>120</v>
       </c>
       <c r="F57" s="1">
@@ -2261,7 +2252,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="13" t="s">
+      <c r="A58" s="12" t="s">
         <v>121</v>
       </c>
       <c r="B58" s="1" t="s">
@@ -2270,7 +2261,7 @@
       <c r="C58" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E58" s="13" t="s">
+      <c r="E58" s="12" t="s">
         <v>122</v>
       </c>
       <c r="F58" s="1">
@@ -2278,7 +2269,7 @@
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="17" t="s">
+      <c r="A59" s="16" t="s">
         <v>123</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -2287,7 +2278,7 @@
       <c r="C59" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E59" s="19" t="s">
+      <c r="E59" s="18" t="s">
         <v>124</v>
       </c>
       <c r="F59" s="1">
@@ -2295,7 +2286,7 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="15" t="s">
+      <c r="A60" s="14" t="s">
         <v>125</v>
       </c>
       <c r="B60" s="1" t="s">
@@ -2304,7 +2295,7 @@
       <c r="C60" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E60" s="13" t="s">
+      <c r="E60" s="12" t="s">
         <v>126</v>
       </c>
       <c r="F60" s="1">
@@ -2312,7 +2303,7 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="13" t="s">
+      <c r="A61" s="12" t="s">
         <v>127</v>
       </c>
       <c r="B61" s="1" t="s">
@@ -2321,7 +2312,7 @@
       <c r="C61" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E61" s="13" t="s">
+      <c r="E61" s="12" t="s">
         <v>128</v>
       </c>
       <c r="F61" s="1">
@@ -2329,7 +2320,7 @@
       </c>
     </row>
     <row r="62" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="15" t="s">
+      <c r="A62" s="14" t="s">
         <v>129</v>
       </c>
       <c r="B62" s="1" t="s">
@@ -2338,7 +2329,7 @@
       <c r="C62" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E62" s="13" t="s">
+      <c r="E62" s="12" t="s">
         <v>130</v>
       </c>
       <c r="F62" s="1">
@@ -2346,7 +2337,7 @@
       </c>
     </row>
     <row r="63" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="17" t="s">
+      <c r="A63" s="16" t="s">
         <v>131</v>
       </c>
       <c r="B63" s="1" t="s">
@@ -2355,7 +2346,7 @@
       <c r="C63" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E63" s="13" t="s">
+      <c r="E63" s="12" t="s">
         <v>132</v>
       </c>
       <c r="F63" s="1">
@@ -2363,7 +2354,7 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A64" s="13" t="s">
+      <c r="A64" s="12" t="s">
         <v>133</v>
       </c>
       <c r="B64" s="1" t="s">
@@ -2372,7 +2363,7 @@
       <c r="C64" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E64" s="13" t="s">
+      <c r="E64" s="12" t="s">
         <v>134</v>
       </c>
       <c r="F64" s="1">
@@ -2380,7 +2371,7 @@
       </c>
     </row>
     <row r="65" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="17" t="s">
+      <c r="A65" s="16" t="s">
         <v>136</v>
       </c>
       <c r="B65" s="1" t="s">
@@ -2389,15 +2380,15 @@
       <c r="C65" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E65" s="17" t="s">
+      <c r="E65" s="16" t="s">
         <v>137</v>
       </c>
       <c r="F65" s="1">
-        <v>1111</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="13" t="s">
+      <c r="A66" s="12" t="s">
         <v>138</v>
       </c>
       <c r="B66" s="1" t="s">
@@ -2406,15 +2397,15 @@
       <c r="C66" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E66" s="13" t="s">
+      <c r="E66" s="12" t="s">
         <v>139</v>
       </c>
       <c r="F66" s="1">
-        <v>1111</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="13" t="s">
+      <c r="A67" s="12" t="s">
         <v>140</v>
       </c>
       <c r="B67" s="1" t="s">
@@ -2426,7 +2417,7 @@
       <c r="D67" s="2">
         <v>393249025348</v>
       </c>
-      <c r="E67" s="16" t="s">
+      <c r="E67" s="15" t="s">
         <v>141</v>
       </c>
       <c r="F67" s="1">
@@ -2434,7 +2425,7 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A68" s="13" t="s">
+      <c r="A68" s="12" t="s">
         <v>241</v>
       </c>
       <c r="B68" s="1" t="s">
@@ -2446,7 +2437,7 @@
       <c r="D68" s="2">
         <v>393476870641</v>
       </c>
-      <c r="E68" s="13" t="s">
+      <c r="E68" s="12" t="s">
         <v>142</v>
       </c>
       <c r="F68" s="1">
@@ -2454,7 +2445,7 @@
       </c>
     </row>
     <row r="69" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A69" s="13" t="s">
+      <c r="A69" s="12" t="s">
         <v>143</v>
       </c>
       <c r="B69" s="1" t="s">
@@ -2463,7 +2454,7 @@
       <c r="C69" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E69" s="13" t="s">
+      <c r="E69" s="12" t="s">
         <v>144</v>
       </c>
       <c r="F69" s="1">
@@ -2471,7 +2462,7 @@
       </c>
     </row>
     <row r="70" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A70" s="15" t="s">
+      <c r="A70" s="14" t="s">
         <v>145</v>
       </c>
       <c r="B70" s="1" t="s">
@@ -2480,7 +2471,7 @@
       <c r="C70" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E70" s="15" t="s">
+      <c r="E70" s="14" t="s">
         <v>146</v>
       </c>
       <c r="F70" s="1">
@@ -2488,7 +2479,7 @@
       </c>
     </row>
     <row r="71" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A71" s="13" t="s">
+      <c r="A71" s="12" t="s">
         <v>147</v>
       </c>
       <c r="B71" s="1" t="s">
@@ -2497,7 +2488,7 @@
       <c r="C71" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E71" s="13" t="s">
+      <c r="E71" s="12" t="s">
         <v>148</v>
       </c>
       <c r="F71" s="1">
@@ -2505,7 +2496,7 @@
       </c>
     </row>
     <row r="72" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A72" s="15" t="s">
+      <c r="A72" s="14" t="s">
         <v>149</v>
       </c>
       <c r="B72" s="1" t="s">
@@ -2514,7 +2505,7 @@
       <c r="C72" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E72" s="13" t="s">
+      <c r="E72" s="12" t="s">
         <v>150</v>
       </c>
       <c r="F72" s="1">
@@ -2522,7 +2513,7 @@
       </c>
     </row>
     <row r="73" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="17" t="s">
+      <c r="A73" s="16" t="s">
         <v>151</v>
       </c>
       <c r="B73" s="1" t="s">
@@ -2531,7 +2522,7 @@
       <c r="C73" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E73" s="17" t="s">
+      <c r="E73" s="16" t="s">
         <v>152</v>
       </c>
       <c r="F73" s="1">
@@ -2539,7 +2530,7 @@
       </c>
     </row>
     <row r="74" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="17" t="s">
+      <c r="A74" s="16" t="s">
         <v>153</v>
       </c>
       <c r="B74" s="1" t="s">
@@ -2548,7 +2539,7 @@
       <c r="C74" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E74" s="19" t="s">
+      <c r="E74" s="18" t="s">
         <v>154</v>
       </c>
       <c r="F74" s="1">
@@ -2556,7 +2547,7 @@
       </c>
     </row>
     <row r="75" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A75" s="16" t="s">
+      <c r="A75" s="15" t="s">
         <v>155</v>
       </c>
       <c r="B75" s="1" t="s">
@@ -2565,7 +2556,7 @@
       <c r="C75" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E75" s="18" t="s">
+      <c r="E75" s="17" t="s">
         <v>156</v>
       </c>
       <c r="F75" s="1">
@@ -2573,7 +2564,7 @@
       </c>
     </row>
     <row r="76" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="15" t="s">
+      <c r="A76" s="14" t="s">
         <v>157</v>
       </c>
       <c r="B76" s="1" t="s">
@@ -2582,7 +2573,7 @@
       <c r="C76" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E76" s="13" t="s">
+      <c r="E76" s="12" t="s">
         <v>158</v>
       </c>
       <c r="F76" s="1">
@@ -2590,7 +2581,7 @@
       </c>
     </row>
     <row r="77" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A77" s="13" t="s">
+      <c r="A77" s="12" t="s">
         <v>160</v>
       </c>
       <c r="B77" s="1" t="s">
@@ -2599,15 +2590,15 @@
       <c r="C77" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E77" s="13" t="s">
+      <c r="E77" s="12" t="s">
         <v>161</v>
       </c>
       <c r="F77" s="1">
-        <v>1111</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A78" s="13" t="s">
+      <c r="A78" s="12" t="s">
         <v>162</v>
       </c>
       <c r="B78" s="1" t="s">
@@ -2616,7 +2607,7 @@
       <c r="C78" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E78" s="13" t="s">
+      <c r="E78" s="12" t="s">
         <v>163</v>
       </c>
       <c r="F78" s="1">
@@ -2624,7 +2615,7 @@
       </c>
     </row>
     <row r="79" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="16" t="s">
+      <c r="A79" s="15" t="s">
         <v>164</v>
       </c>
       <c r="B79" s="1" t="s">
@@ -2633,7 +2624,7 @@
       <c r="C79" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E79" s="16" t="s">
+      <c r="E79" s="15" t="s">
         <v>165</v>
       </c>
       <c r="F79" s="1">
@@ -2641,7 +2632,7 @@
       </c>
     </row>
     <row r="80" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="13" t="s">
+      <c r="A80" s="12" t="s">
         <v>166</v>
       </c>
       <c r="B80" s="1" t="s">
@@ -2650,7 +2641,7 @@
       <c r="C80" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E80" s="13" t="s">
+      <c r="E80" s="12" t="s">
         <v>167</v>
       </c>
       <c r="F80" s="1">
@@ -2658,7 +2649,7 @@
       </c>
     </row>
     <row r="81" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A81" s="15" t="s">
+      <c r="A81" s="14" t="s">
         <v>168</v>
       </c>
       <c r="B81" s="1" t="s">
@@ -2667,7 +2658,7 @@
       <c r="C81" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E81" s="15" t="s">
+      <c r="E81" s="14" t="s">
         <v>169</v>
       </c>
       <c r="F81" s="1">
@@ -2675,7 +2666,7 @@
       </c>
     </row>
     <row r="82" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A82" s="16" t="s">
+      <c r="A82" s="15" t="s">
         <v>170</v>
       </c>
       <c r="B82" s="1" t="s">
@@ -2684,7 +2675,7 @@
       <c r="C82" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E82" s="18" t="s">
+      <c r="E82" s="17" t="s">
         <v>171</v>
       </c>
       <c r="F82" s="1">
@@ -2692,7 +2683,7 @@
       </c>
     </row>
     <row r="83" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A83" s="13" t="s">
+      <c r="A83" s="12" t="s">
         <v>172</v>
       </c>
       <c r="B83" s="1" t="s">
@@ -2701,7 +2692,7 @@
       <c r="C83" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E83" s="13" t="s">
+      <c r="E83" s="12" t="s">
         <v>173</v>
       </c>
       <c r="F83" s="1">
@@ -2709,7 +2700,7 @@
       </c>
     </row>
     <row r="84" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A84" s="13" t="s">
+      <c r="A84" s="12" t="s">
         <v>174</v>
       </c>
       <c r="B84" s="1" t="s">
@@ -2718,7 +2709,7 @@
       <c r="C84" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E84" s="16" t="s">
+      <c r="E84" s="15" t="s">
         <v>175</v>
       </c>
       <c r="F84" s="1">
@@ -2726,7 +2717,7 @@
       </c>
     </row>
     <row r="85" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A85" s="17" t="s">
+      <c r="A85" s="16" t="s">
         <v>176</v>
       </c>
       <c r="B85" s="1" t="s">
@@ -2735,15 +2726,15 @@
       <c r="C85" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E85" s="18" t="s">
+      <c r="E85" s="17" t="s">
         <v>177</v>
       </c>
       <c r="F85" s="1">
-        <v>1111</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A86" s="15" t="s">
+      <c r="A86" s="14" t="s">
         <v>178</v>
       </c>
       <c r="B86" s="1" t="s">
@@ -2752,7 +2743,7 @@
       <c r="C86" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E86" s="13" t="s">
+      <c r="E86" s="12" t="s">
         <v>179</v>
       </c>
       <c r="F86" s="1">
@@ -2760,7 +2751,7 @@
       </c>
     </row>
     <row r="87" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A87" s="17" t="s">
+      <c r="A87" s="16" t="s">
         <v>180</v>
       </c>
       <c r="B87" s="1" t="s">
@@ -2769,7 +2760,7 @@
       <c r="C87" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E87" s="19" t="s">
+      <c r="E87" s="18" t="s">
         <v>181</v>
       </c>
       <c r="F87" s="1">
@@ -2777,7 +2768,7 @@
       </c>
     </row>
     <row r="88" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A88" s="15" t="s">
+      <c r="A88" s="14" t="s">
         <v>182</v>
       </c>
       <c r="B88" s="1" t="s">
@@ -2786,7 +2777,7 @@
       <c r="C88" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E88" s="16" t="s">
+      <c r="E88" s="15" t="s">
         <v>183</v>
       </c>
       <c r="F88" s="1">
@@ -2794,7 +2785,7 @@
       </c>
     </row>
     <row r="89" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A89" s="13" t="s">
+      <c r="A89" s="12" t="s">
         <v>184</v>
       </c>
       <c r="B89" s="1" t="s">
@@ -2803,7 +2794,7 @@
       <c r="C89" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="E89" s="13" t="s">
+      <c r="E89" s="12" t="s">
         <v>185</v>
       </c>
       <c r="F89" s="1">
@@ -2811,7 +2802,7 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A90" s="13" t="s">
+      <c r="A90" s="12" t="s">
         <v>187</v>
       </c>
       <c r="B90" s="1" t="s">
@@ -2823,15 +2814,15 @@
       <c r="D90" s="2">
         <v>393297735084</v>
       </c>
-      <c r="E90" s="16" t="s">
+      <c r="E90" s="15" t="s">
         <v>188</v>
       </c>
       <c r="F90" s="1">
-        <v>1111</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A91" s="13" t="s">
+      <c r="A91" s="12" t="s">
         <v>189</v>
       </c>
       <c r="B91" s="1" t="s">
@@ -2843,15 +2834,15 @@
       <c r="D91" s="2">
         <v>393281527839</v>
       </c>
-      <c r="E91" s="13" t="s">
+      <c r="E91" s="12" t="s">
         <v>190</v>
       </c>
       <c r="F91" s="1">
-        <v>1111</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" s="17" t="s">
+      <c r="A92" s="16" t="s">
         <v>191</v>
       </c>
       <c r="B92" s="1" t="s">
@@ -2863,7 +2854,7 @@
       <c r="D92" s="2">
         <v>393337039626</v>
       </c>
-      <c r="E92" s="17" t="s">
+      <c r="E92" s="16" t="s">
         <v>192</v>
       </c>
       <c r="F92" s="1">
@@ -2871,7 +2862,7 @@
       </c>
     </row>
     <row r="93" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="17" t="s">
+      <c r="A93" s="16" t="s">
         <v>193</v>
       </c>
       <c r="B93" s="1" t="s">
@@ -2883,7 +2874,7 @@
       <c r="D93" s="2">
         <v>393668993714</v>
       </c>
-      <c r="E93" s="17" t="s">
+      <c r="E93" s="16" t="s">
         <v>194</v>
       </c>
       <c r="F93" s="1">
@@ -2891,7 +2882,7 @@
       </c>
     </row>
     <row r="94" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A94" s="13" t="s">
+      <c r="A94" s="12" t="s">
         <v>195</v>
       </c>
       <c r="B94" s="1" t="s">
@@ -2903,7 +2894,7 @@
       <c r="D94" s="2">
         <v>393273997950</v>
       </c>
-      <c r="E94" s="13" t="s">
+      <c r="E94" s="12" t="s">
         <v>196</v>
       </c>
       <c r="F94" s="1">
@@ -2911,7 +2902,7 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A95" s="13" t="s">
+      <c r="A95" s="12" t="s">
         <v>197</v>
       </c>
       <c r="B95" s="1" t="s">
@@ -2923,7 +2914,7 @@
       <c r="D95" s="2">
         <v>393316298506</v>
       </c>
-      <c r="E95" s="13" t="s">
+      <c r="E95" s="12" t="s">
         <v>198</v>
       </c>
       <c r="F95" s="1">
@@ -2931,7 +2922,7 @@
       </c>
     </row>
     <row r="96" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A96" s="13" t="s">
+      <c r="A96" s="12" t="s">
         <v>199</v>
       </c>
       <c r="B96" s="1" t="s">
@@ -2943,7 +2934,7 @@
       <c r="D96" s="2">
         <v>393343140500</v>
       </c>
-      <c r="E96" s="13" t="s">
+      <c r="E96" s="12" t="s">
         <v>200</v>
       </c>
       <c r="F96" s="1">
@@ -2951,7 +2942,7 @@
       </c>
     </row>
     <row r="97" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A97" s="13" t="s">
+      <c r="A97" s="12" t="s">
         <v>201</v>
       </c>
       <c r="B97" s="1" t="s">
@@ -2963,7 +2954,7 @@
       <c r="D97" s="2">
         <v>393351612468</v>
       </c>
-      <c r="E97" s="16" t="s">
+      <c r="E97" s="15" t="s">
         <v>202</v>
       </c>
       <c r="F97" s="1">
@@ -2971,7 +2962,7 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A98" s="15" t="s">
+      <c r="A98" s="14" t="s">
         <v>203</v>
       </c>
       <c r="B98" s="1" t="s">
@@ -2983,7 +2974,7 @@
       <c r="D98" s="2">
         <v>393402901672</v>
       </c>
-      <c r="E98" s="15" t="s">
+      <c r="E98" s="14" t="s">
         <v>204</v>
       </c>
       <c r="F98" s="1">
@@ -2991,7 +2982,7 @@
       </c>
     </row>
     <row r="99" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A99" s="15" t="s">
+      <c r="A99" s="14" t="s">
         <v>205</v>
       </c>
       <c r="B99" s="1" t="s">
@@ -3003,7 +2994,7 @@
       <c r="D99" s="2">
         <v>393510837400</v>
       </c>
-      <c r="E99" s="13" t="s">
+      <c r="E99" s="12" t="s">
         <v>206</v>
       </c>
       <c r="F99" s="1">
@@ -3011,7 +3002,7 @@
       </c>
     </row>
     <row r="100" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A100" s="13" t="s">
+      <c r="A100" s="12" t="s">
         <v>207</v>
       </c>
       <c r="B100" s="1" t="s">
@@ -3023,7 +3014,7 @@
       <c r="D100" s="2">
         <v>393421215671</v>
       </c>
-      <c r="E100" s="13" t="s">
+      <c r="E100" s="12" t="s">
         <v>208</v>
       </c>
       <c r="F100" s="1">
@@ -3031,7 +3022,7 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A101" s="13" t="s">
+      <c r="A101" s="12" t="s">
         <v>209</v>
       </c>
       <c r="B101" s="1" t="s">
@@ -3043,7 +3034,7 @@
       <c r="D101" s="2">
         <v>393313969976</v>
       </c>
-      <c r="E101" s="13" t="s">
+      <c r="E101" s="12" t="s">
         <v>210</v>
       </c>
       <c r="F101" s="1">
@@ -3051,7 +3042,7 @@
       </c>
     </row>
     <row r="102" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A102" s="13" t="s">
+      <c r="A102" s="12" t="s">
         <v>212</v>
       </c>
       <c r="B102" s="1" t="s">
@@ -3060,15 +3051,15 @@
       <c r="C102" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="E102" s="13" t="s">
+      <c r="E102" s="12" t="s">
         <v>213</v>
       </c>
       <c r="F102" s="1">
-        <v>1111</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A103" s="13" t="s">
+      <c r="A103" s="12" t="s">
         <v>214</v>
       </c>
       <c r="B103" s="1" t="s">
@@ -3077,15 +3068,15 @@
       <c r="C103" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="E103" s="13" t="s">
+      <c r="E103" s="12" t="s">
         <v>215</v>
       </c>
       <c r="F103" s="1">
-        <v>1111</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A104" s="13" t="s">
+      <c r="A104" s="12" t="s">
         <v>216</v>
       </c>
       <c r="B104" s="1" t="s">
@@ -3094,7 +3085,7 @@
       <c r="C104" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="E104" s="13" t="s">
+      <c r="E104" s="12" t="s">
         <v>217</v>
       </c>
       <c r="F104" s="1">
@@ -3102,7 +3093,7 @@
       </c>
     </row>
     <row r="105" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="16" t="s">
+      <c r="A105" s="15" t="s">
         <v>218</v>
       </c>
       <c r="B105" s="1" t="s">
@@ -3111,7 +3102,7 @@
       <c r="C105" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="E105" s="18" t="s">
+      <c r="E105" s="17" t="s">
         <v>219</v>
       </c>
       <c r="F105" s="1">
@@ -3119,7 +3110,7 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A106" s="13" t="s">
+      <c r="A106" s="12" t="s">
         <v>220</v>
       </c>
       <c r="B106" s="1" t="s">
@@ -3128,7 +3119,7 @@
       <c r="C106" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="E106" s="13" t="s">
+      <c r="E106" s="12" t="s">
         <v>221</v>
       </c>
       <c r="F106" s="1">
@@ -3136,7 +3127,7 @@
       </c>
     </row>
     <row r="107" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A107" s="13" t="s">
+      <c r="A107" s="12" t="s">
         <v>222</v>
       </c>
       <c r="B107" s="1" t="s">
@@ -3145,7 +3136,7 @@
       <c r="C107" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="E107" s="13" t="s">
+      <c r="E107" s="12" t="s">
         <v>223</v>
       </c>
       <c r="F107" s="1">
@@ -3153,7 +3144,7 @@
       </c>
     </row>
     <row r="108" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A108" s="15" t="s">
+      <c r="A108" s="14" t="s">
         <v>224</v>
       </c>
       <c r="B108" s="1" t="s">
@@ -3162,7 +3153,7 @@
       <c r="C108" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="E108" s="15" t="s">
+      <c r="E108" s="14" t="s">
         <v>225</v>
       </c>
       <c r="F108" s="1">
@@ -3170,7 +3161,7 @@
       </c>
     </row>
     <row r="109" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A109" s="13" t="s">
+      <c r="A109" s="12" t="s">
         <v>226</v>
       </c>
       <c r="B109" s="1" t="s">
@@ -3179,7 +3170,7 @@
       <c r="C109" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="E109" s="13" t="s">
+      <c r="E109" s="12" t="s">
         <v>227</v>
       </c>
       <c r="F109" s="1">
@@ -3187,7 +3178,7 @@
       </c>
     </row>
     <row r="110" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A110" s="13" t="s">
+      <c r="A110" s="12" t="s">
         <v>228</v>
       </c>
       <c r="B110" s="1" t="s">
@@ -3196,7 +3187,7 @@
       <c r="C110" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="E110" s="13" t="s">
+      <c r="E110" s="12" t="s">
         <v>229</v>
       </c>
       <c r="F110" s="1">
@@ -3204,7 +3195,7 @@
       </c>
     </row>
     <row r="111" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A111" s="20" t="s">
+      <c r="A111" s="19" t="s">
         <v>230</v>
       </c>
       <c r="B111" s="1" t="s">
@@ -3213,7 +3204,7 @@
       <c r="C111" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="E111" s="20" t="s">
+      <c r="E111" s="19" t="s">
         <v>231</v>
       </c>
       <c r="F111" s="1">
@@ -3221,7 +3212,7 @@
       </c>
     </row>
     <row r="112" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A112" s="15" t="s">
+      <c r="A112" s="14" t="s">
         <v>232</v>
       </c>
       <c r="B112" s="1" t="s">
@@ -3230,7 +3221,7 @@
       <c r="C112" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="E112" s="13" t="s">
+      <c r="E112" s="12" t="s">
         <v>233</v>
       </c>
       <c r="F112" s="1">
@@ -3238,7 +3229,7 @@
       </c>
     </row>
     <row r="113" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A113" s="15" t="s">
+      <c r="A113" s="14" t="s">
         <v>234</v>
       </c>
       <c r="B113" s="1" t="s">
@@ -3247,7 +3238,7 @@
       <c r="C113" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="E113" s="13" t="s">
+      <c r="E113" s="12" t="s">
         <v>235</v>
       </c>
       <c r="F113" s="1">
@@ -3255,7 +3246,7 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" s="6" t="s">
+      <c r="A114" s="5" t="s">
         <v>240</v>
       </c>
       <c r="B114" s="1" t="s">
